--- a/research/traditional_assets/database/data/lithuania/lithuania_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0748875544066695</v>
+        <v>0.07481347307505948</v>
       </c>
       <c r="C2">
-        <v>1095.150568803853</v>
+        <v>1085.331309065787</v>
       </c>
       <c r="D2">
-        <v>1088.310568803853</v>
+        <v>1089.4233728521</v>
       </c>
       <c r="E2">
-        <v>-143.2063786313322</v>
+        <v>-132.2743148450189</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.93206378631332</v>
       </c>
       <c r="G2">
         <v>6.84</v>
@@ -1451,28 +1451,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.54988280845156</v>
       </c>
       <c r="N2">
-        <v>85.11000000000001</v>
+        <v>84.56011719154846</v>
       </c>
       <c r="O2">
-        <v>12.7665</v>
+        <v>12.68401757873227</v>
       </c>
       <c r="P2">
-        <v>72.34350000000001</v>
+        <v>71.87609961281619</v>
       </c>
       <c r="Q2">
-        <v>169.4435</v>
+        <v>168.9760996128162</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0748875544066695</v>
+        <v>0.07513729603541362</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.537322879721409</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.7784340442741</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07481347307505948</v>
+        <v>0.07473939174344947</v>
       </c>
       <c r="C3">
-        <v>1085.331309065787</v>
+        <v>1075.514327354571</v>
       </c>
       <c r="D3">
-        <v>1089.4233728521</v>
+        <v>1090.538454927198</v>
       </c>
       <c r="E3">
-        <v>-132.2743148450189</v>
+        <v>-121.3422510587056</v>
       </c>
       <c r="F3">
-        <v>10.93206378631332</v>
+        <v>21.86412757262664</v>
       </c>
       <c r="G3">
         <v>6.84</v>
@@ -1533,28 +1533,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M3">
-        <v>0.54988280845156</v>
+        <v>1.09976561690312</v>
       </c>
       <c r="N3">
-        <v>84.56011719154846</v>
+        <v>84.0102343830969</v>
       </c>
       <c r="O3">
-        <v>12.68401757873227</v>
+        <v>12.60153515746453</v>
       </c>
       <c r="P3">
-        <v>71.87609961281619</v>
+        <v>71.40869922563236</v>
       </c>
       <c r="Q3">
-        <v>168.9760996128162</v>
+        <v>168.5086992256324</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07513729603541362</v>
+        <v>0.07539213443209131</v>
       </c>
       <c r="T3">
-        <v>0.537322879721409</v>
+        <v>0.5419903344521092</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.7784340442741</v>
+        <v>77.38921702213707</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07473939174344947</v>
+        <v>0.07466531041183948</v>
       </c>
       <c r="C4">
-        <v>1075.514327354571</v>
+        <v>1065.699630672413</v>
       </c>
       <c r="D4">
-        <v>1090.538454927198</v>
+        <v>1091.655822031353</v>
       </c>
       <c r="E4">
-        <v>-121.3422510587056</v>
+        <v>-110.4101872723923</v>
       </c>
       <c r="F4">
-        <v>21.86412757262664</v>
+        <v>32.79619135893996</v>
       </c>
       <c r="G4">
         <v>6.84</v>
@@ -1615,28 +1615,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M4">
-        <v>1.09976561690312</v>
+        <v>1.64964842535468</v>
       </c>
       <c r="N4">
-        <v>84.0102343830969</v>
+        <v>83.46035157464533</v>
       </c>
       <c r="O4">
-        <v>12.60153515746453</v>
+        <v>12.5190527361968</v>
       </c>
       <c r="P4">
-        <v>71.40869922563236</v>
+        <v>70.94129883844853</v>
       </c>
       <c r="Q4">
-        <v>168.5086992256324</v>
+        <v>168.0412988384485</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07539213443209131</v>
+        <v>0.07565222722870049</v>
       </c>
       <c r="T4">
-        <v>0.5419903344521092</v>
+        <v>0.5467540253628237</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.38921702213707</v>
+        <v>51.59281134809137</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07466531041183948</v>
+        <v>0.07459122908022947</v>
       </c>
       <c r="C5">
-        <v>1065.699630672413</v>
+        <v>1055.887226050249</v>
       </c>
       <c r="D5">
-        <v>1091.655822031353</v>
+        <v>1092.775481195502</v>
       </c>
       <c r="E5">
-        <v>-110.4101872723923</v>
+        <v>-99.47812348607894</v>
       </c>
       <c r="F5">
-        <v>32.79619135893996</v>
+        <v>43.72825514525329</v>
       </c>
       <c r="G5">
         <v>6.84</v>
@@ -1697,28 +1697,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M5">
-        <v>1.64964842535468</v>
+        <v>2.19953123380624</v>
       </c>
       <c r="N5">
-        <v>83.46035157464533</v>
+        <v>82.91046876619377</v>
       </c>
       <c r="O5">
-        <v>12.5190527361968</v>
+        <v>12.43657031492907</v>
       </c>
       <c r="P5">
-        <v>70.94129883844853</v>
+        <v>70.4738984512647</v>
       </c>
       <c r="Q5">
-        <v>168.0412988384485</v>
+        <v>167.5738984512647</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07565222722870049</v>
+        <v>0.07591773862523904</v>
       </c>
       <c r="T5">
-        <v>0.5467540253628237</v>
+        <v>0.5516169598341781</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.59281134809137</v>
+        <v>38.69460851106854</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07459122908022947</v>
+        <v>0.07451714774861945</v>
       </c>
       <c r="C6">
-        <v>1055.887226050249</v>
+        <v>1046.077120547887</v>
       </c>
       <c r="D6">
-        <v>1092.775481195502</v>
+        <v>1093.897439479453</v>
       </c>
       <c r="E6">
-        <v>-99.47812348607894</v>
+        <v>-88.54605969976561</v>
       </c>
       <c r="F6">
-        <v>43.72825514525329</v>
+        <v>54.66031893156661</v>
       </c>
       <c r="G6">
         <v>6.84</v>
@@ -1779,28 +1779,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M6">
-        <v>2.19953123380624</v>
+        <v>2.749414042257801</v>
       </c>
       <c r="N6">
-        <v>82.91046876619377</v>
+        <v>82.36058595774222</v>
       </c>
       <c r="O6">
-        <v>12.43657031492907</v>
+        <v>12.35408789366133</v>
       </c>
       <c r="P6">
-        <v>70.4738984512647</v>
+        <v>70.00649806408089</v>
       </c>
       <c r="Q6">
-        <v>167.5738984512647</v>
+        <v>167.1064980640809</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07591773862523904</v>
+        <v>0.07618883973538891</v>
       </c>
       <c r="T6">
-        <v>0.5516169598341781</v>
+        <v>0.5565822718733505</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.69460851106854</v>
+        <v>30.95568680885482</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07451714774861945</v>
+        <v>0.07444306641700946</v>
       </c>
       <c r="C7">
-        <v>1046.077120547887</v>
+        <v>1036.26932125416</v>
       </c>
       <c r="D7">
-        <v>1093.897439479453</v>
+        <v>1095.02170397204</v>
       </c>
       <c r="E7">
-        <v>-88.54605969976561</v>
+        <v>-77.61399591345229</v>
       </c>
       <c r="F7">
-        <v>54.66031893156661</v>
+        <v>65.59238271787994</v>
       </c>
       <c r="G7">
         <v>6.84</v>
@@ -1861,28 +1861,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M7">
-        <v>2.749414042257801</v>
+        <v>3.299296850709361</v>
       </c>
       <c r="N7">
-        <v>82.36058595774222</v>
+        <v>81.81070314929065</v>
       </c>
       <c r="O7">
-        <v>12.35408789366133</v>
+        <v>12.2716054723936</v>
       </c>
       <c r="P7">
-        <v>70.00649806408089</v>
+        <v>69.53909767689704</v>
       </c>
       <c r="Q7">
-        <v>167.1064980640809</v>
+        <v>166.6390976768971</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07618883973538891</v>
+        <v>0.07646570895426538</v>
       </c>
       <c r="T7">
-        <v>0.5565822718733505</v>
+        <v>0.5616532288495266</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.95568680885482</v>
+        <v>25.79640567404568</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07444306641700946</v>
+        <v>0.07436898508539946</v>
       </c>
       <c r="C8">
-        <v>1036.26932125416</v>
+        <v>1026.463835287075</v>
       </c>
       <c r="D8">
-        <v>1095.02170397204</v>
+        <v>1096.148281791269</v>
       </c>
       <c r="E8">
-        <v>-77.6139959134523</v>
+        <v>-66.68193212713898</v>
       </c>
       <c r="F8">
-        <v>65.59238271787993</v>
+        <v>76.52444650419325</v>
       </c>
       <c r="G8">
         <v>6.84</v>
@@ -1943,28 +1943,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M8">
-        <v>3.29929685070936</v>
+        <v>3.84917965916092</v>
       </c>
       <c r="N8">
-        <v>81.81070314929066</v>
+        <v>81.26082034083909</v>
       </c>
       <c r="O8">
-        <v>12.2716054723936</v>
+        <v>12.18912305112586</v>
       </c>
       <c r="P8">
-        <v>69.53909767689706</v>
+        <v>69.07169728971323</v>
       </c>
       <c r="Q8">
-        <v>166.6390976768971</v>
+        <v>166.1716972897132</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07646570895426538</v>
+        <v>0.07674853234989189</v>
       </c>
       <c r="T8">
-        <v>0.5616532288495266</v>
+        <v>0.5668332386639</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.79640567404569</v>
+        <v>22.11120486346773</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07436898508539945</v>
+        <v>0.07429490375378947</v>
       </c>
       <c r="C9">
-        <v>1026.463835287076</v>
+        <v>1016.66066979396</v>
       </c>
       <c r="D9">
-        <v>1096.148281791269</v>
+        <v>1097.277180084466</v>
       </c>
       <c r="E9">
-        <v>-66.68193212713896</v>
+        <v>-55.74986834082566</v>
       </c>
       <c r="F9">
-        <v>76.52444650419326</v>
+        <v>87.45651029050657</v>
       </c>
       <c r="G9">
         <v>6.84</v>
@@ -2025,28 +2025,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M9">
-        <v>3.849179659160921</v>
+        <v>4.39906246761248</v>
       </c>
       <c r="N9">
-        <v>81.26082034083909</v>
+        <v>80.71093753238753</v>
       </c>
       <c r="O9">
-        <v>12.18912305112586</v>
+        <v>12.10664062985813</v>
       </c>
       <c r="P9">
-        <v>69.07169728971323</v>
+        <v>68.6042969025294</v>
       </c>
       <c r="Q9">
-        <v>166.1716972897132</v>
+        <v>165.7042969025294</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07674853234989189</v>
+        <v>0.07703750408020593</v>
       </c>
       <c r="T9">
-        <v>0.5668332386639</v>
+        <v>0.5721258573872816</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.11120486346773</v>
+        <v>19.34730425553427</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07429490375378947</v>
+        <v>0.07422082242217945</v>
       </c>
       <c r="C10">
-        <v>1016.66066979396</v>
+        <v>1006.859831951616</v>
       </c>
       <c r="D10">
-        <v>1097.277180084466</v>
+        <v>1098.408406028436</v>
       </c>
       <c r="E10">
-        <v>-55.74986834082566</v>
+        <v>-44.81780455451234</v>
       </c>
       <c r="F10">
-        <v>87.45651029050657</v>
+        <v>98.38857407681989</v>
       </c>
       <c r="G10">
         <v>6.84</v>
@@ -2107,28 +2107,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M10">
-        <v>4.39906246761248</v>
+        <v>4.94894527606404</v>
       </c>
       <c r="N10">
-        <v>80.71093753238753</v>
+        <v>80.16105472393598</v>
       </c>
       <c r="O10">
-        <v>12.10664062985813</v>
+        <v>12.0241582085904</v>
       </c>
       <c r="P10">
-        <v>68.6042969025294</v>
+        <v>68.13689651534558</v>
       </c>
       <c r="Q10">
-        <v>165.7042969025294</v>
+        <v>165.2368965153456</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07703750408020593</v>
+        <v>0.07733282683755983</v>
       </c>
       <c r="T10">
-        <v>0.5721258573872816</v>
+        <v>0.5775347974012869</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.34730425553427</v>
+        <v>17.19760378269713</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07422082242217945</v>
+        <v>0.07414674109056946</v>
       </c>
       <c r="C11">
-        <v>1006.859831951616</v>
+        <v>997.0613289664714</v>
       </c>
       <c r="D11">
-        <v>1098.408406028436</v>
+        <v>1099.541966829605</v>
       </c>
       <c r="E11">
-        <v>-44.81780455451234</v>
+        <v>-33.88574076819901</v>
       </c>
       <c r="F11">
-        <v>98.38857407681989</v>
+        <v>109.3206378631332</v>
       </c>
       <c r="G11">
         <v>6.84</v>
@@ -2189,28 +2189,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M11">
-        <v>4.94894527606404</v>
+        <v>5.4988280845156</v>
       </c>
       <c r="N11">
-        <v>80.16105472393598</v>
+        <v>79.61117191548442</v>
       </c>
       <c r="O11">
-        <v>12.0241582085904</v>
+        <v>11.94167578732266</v>
       </c>
       <c r="P11">
-        <v>68.13689651534558</v>
+        <v>67.66949612816175</v>
       </c>
       <c r="Q11">
-        <v>165.2368965153456</v>
+        <v>164.7694961281617</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07733282683755983</v>
+        <v>0.07763471232285495</v>
       </c>
       <c r="T11">
-        <v>0.5775347974012869</v>
+        <v>0.5830639360822701</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.19760378269713</v>
+        <v>15.47784340442741</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07414674109056946</v>
+        <v>0.07407265975895945</v>
       </c>
       <c r="C12">
-        <v>997.0613289664714</v>
+        <v>987.265168074733</v>
       </c>
       <c r="D12">
-        <v>1099.541966829605</v>
+        <v>1100.67786972418</v>
       </c>
       <c r="E12">
-        <v>-33.885740768199</v>
+        <v>-22.95367698188569</v>
       </c>
       <c r="F12">
-        <v>109.3206378631332</v>
+        <v>120.2527016494465</v>
       </c>
       <c r="G12">
         <v>6.84</v>
@@ -2271,28 +2271,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M12">
-        <v>5.498828084515601</v>
+        <v>6.04871089296716</v>
       </c>
       <c r="N12">
-        <v>79.61117191548442</v>
+        <v>79.06128910703285</v>
       </c>
       <c r="O12">
-        <v>11.94167578732266</v>
+        <v>11.85919336605493</v>
       </c>
       <c r="P12">
-        <v>67.66949612816175</v>
+        <v>67.20209574097792</v>
       </c>
       <c r="Q12">
-        <v>164.7694961281617</v>
+        <v>164.3020957409779</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07763471232285495</v>
+        <v>0.07794338175163983</v>
       </c>
       <c r="T12">
-        <v>0.5830639360822701</v>
+        <v>0.5887173250706912</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.47784340442741</v>
+        <v>14.07076673129765</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07407265975895945</v>
+        <v>0.07399857842734944</v>
       </c>
       <c r="C13">
-        <v>987.265168074733</v>
+        <v>977.4713565425411</v>
       </c>
       <c r="D13">
-        <v>1100.67786972418</v>
+        <v>1101.816121978301</v>
       </c>
       <c r="E13">
-        <v>-22.95367698188569</v>
+        <v>-12.02161319557237</v>
       </c>
       <c r="F13">
-        <v>120.2527016494465</v>
+        <v>131.1847654357599</v>
       </c>
       <c r="G13">
         <v>6.84</v>
@@ -2353,28 +2353,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M13">
-        <v>6.04871089296716</v>
+        <v>6.598593701418721</v>
       </c>
       <c r="N13">
-        <v>79.06128910703285</v>
+        <v>78.51140629858129</v>
       </c>
       <c r="O13">
-        <v>11.85919336605493</v>
+        <v>11.77671094478719</v>
       </c>
       <c r="P13">
-        <v>67.20209574097792</v>
+        <v>66.73469535379409</v>
       </c>
       <c r="Q13">
-        <v>164.3020957409779</v>
+        <v>163.8346953537941</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07794338175163983</v>
+        <v>0.07825906639471528</v>
       </c>
       <c r="T13">
-        <v>0.5887173250706912</v>
+        <v>0.5944992001724854</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.07076673129765</v>
+        <v>12.89820283702284</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07399857842734944</v>
+        <v>0.07409024709573944</v>
       </c>
       <c r="C14">
-        <v>977.4713565425411</v>
+        <v>965.1311581850164</v>
       </c>
       <c r="D14">
-        <v>1101.816121978301</v>
+        <v>1100.40798740709</v>
       </c>
       <c r="E14">
-        <v>-12.02161319557237</v>
+        <v>-1.089549409259035</v>
       </c>
       <c r="F14">
-        <v>131.1847654357599</v>
+        <v>142.1168292220732</v>
       </c>
       <c r="G14">
         <v>6.84</v>
@@ -2435,45 +2435,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M14">
-        <v>6.598593701418721</v>
+        <v>7.361651753703391</v>
       </c>
       <c r="N14">
-        <v>78.51140629858129</v>
+        <v>77.74834824629662</v>
       </c>
       <c r="O14">
-        <v>11.77671094478719</v>
+        <v>11.66225223694449</v>
       </c>
       <c r="P14">
-        <v>66.73469535379409</v>
+        <v>66.08609600935212</v>
       </c>
       <c r="Q14">
-        <v>163.8346953537941</v>
+        <v>163.1860960093521</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07825906639471528</v>
+        <v>0.07858200815602234</v>
       </c>
       <c r="T14">
-        <v>0.5944992001724854</v>
+        <v>0.6004139919432864</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>12.89820283702284</v>
+        <v>11.56126408141816</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07409024709573944</v>
+        <v>0.07402891576412943</v>
       </c>
       <c r="C15">
-        <v>965.1311581850164</v>
+        <v>955.1408143041892</v>
       </c>
       <c r="D15">
-        <v>1100.40798740709</v>
+        <v>1101.349707312576</v>
       </c>
       <c r="E15">
-        <v>-1.089549409259035</v>
+        <v>9.8425143770543</v>
       </c>
       <c r="F15">
-        <v>142.1168292220732</v>
+        <v>153.0488930083865</v>
       </c>
       <c r="G15">
         <v>6.84</v>
@@ -2517,28 +2517,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M15">
-        <v>7.361651753703391</v>
+        <v>7.927932657834422</v>
       </c>
       <c r="N15">
-        <v>77.74834824629662</v>
+        <v>77.1820673421656</v>
       </c>
       <c r="O15">
-        <v>11.66225223694449</v>
+        <v>11.57731010132484</v>
       </c>
       <c r="P15">
-        <v>66.08609600935212</v>
+        <v>65.60475724084075</v>
       </c>
       <c r="Q15">
-        <v>163.1860960093521</v>
+        <v>162.7047572408408</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07858200815602234</v>
+        <v>0.07891246019084817</v>
       </c>
       <c r="T15">
-        <v>0.6004139919432864</v>
+        <v>0.6064663370110827</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.56126408141816</v>
+        <v>10.735459504174</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07402891576412943</v>
+        <v>0.07396758443251943</v>
       </c>
       <c r="C16">
-        <v>955.1408143041892</v>
+        <v>945.1520836358933</v>
       </c>
       <c r="D16">
-        <v>1101.349707312576</v>
+        <v>1102.293040430593</v>
       </c>
       <c r="E16">
-        <v>9.8425143770543</v>
+        <v>20.77457816336764</v>
       </c>
       <c r="F16">
-        <v>153.0488930083865</v>
+        <v>163.9809567946999</v>
       </c>
       <c r="G16">
         <v>6.84</v>
@@ -2599,28 +2599,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M16">
-        <v>7.927932657834422</v>
+        <v>8.494213561965452</v>
       </c>
       <c r="N16">
-        <v>77.1820673421656</v>
+        <v>76.61578643803456</v>
       </c>
       <c r="O16">
-        <v>11.57731010132484</v>
+        <v>11.49236796570518</v>
       </c>
       <c r="P16">
-        <v>65.60475724084075</v>
+        <v>65.12341847232938</v>
       </c>
       <c r="Q16">
-        <v>162.7047572408408</v>
+        <v>162.2234184723294</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07891246019084817</v>
+        <v>0.07925068756766991</v>
       </c>
       <c r="T16">
-        <v>0.6064663370110827</v>
+        <v>0.6126610901981213</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.735459504174</v>
+        <v>10.01976220389574</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07396758443251943</v>
+        <v>0.07413745310090943</v>
       </c>
       <c r="C17">
-        <v>945.1520836358933</v>
+        <v>931.6112321667824</v>
       </c>
       <c r="D17">
-        <v>1102.293040430593</v>
+        <v>1099.684252747796</v>
       </c>
       <c r="E17">
-        <v>20.77457816336761</v>
+        <v>31.70664194968091</v>
       </c>
       <c r="F17">
-        <v>163.9809567946998</v>
+        <v>174.9130205810131</v>
       </c>
       <c r="G17">
         <v>6.84</v>
@@ -2681,45 +2681,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M17">
-        <v>8.49421356196545</v>
+        <v>9.357846601084203</v>
       </c>
       <c r="N17">
-        <v>76.61578643803456</v>
+        <v>75.75215339891581</v>
       </c>
       <c r="O17">
-        <v>11.49236796570518</v>
+        <v>11.36282300983737</v>
       </c>
       <c r="P17">
-        <v>65.12341847232938</v>
+        <v>64.38933038907844</v>
       </c>
       <c r="Q17">
-        <v>162.2234184723294</v>
+        <v>161.4893303890784</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07925068756766991</v>
+        <v>0.07959696797727313</v>
       </c>
       <c r="T17">
-        <v>0.6126610901981213</v>
+        <v>0.619003337508661</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.01976220389574</v>
+        <v>9.095041159377322</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07413745310090943</v>
+        <v>0.07409057176929941</v>
       </c>
       <c r="C18">
-        <v>931.6112321667824</v>
+        <v>921.3979220825995</v>
       </c>
       <c r="D18">
-        <v>1099.684252747796</v>
+        <v>1100.403006449926</v>
       </c>
       <c r="E18">
-        <v>31.70664194968091</v>
+        <v>42.63870573599425</v>
       </c>
       <c r="F18">
-        <v>174.9130205810131</v>
+        <v>185.8450843673265</v>
       </c>
       <c r="G18">
         <v>6.84</v>
@@ -2763,28 +2763,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M18">
-        <v>9.357846601084203</v>
+        <v>9.942712013651967</v>
       </c>
       <c r="N18">
-        <v>75.75215339891581</v>
+        <v>75.16728798634804</v>
       </c>
       <c r="O18">
-        <v>11.36282300983737</v>
+        <v>11.27509319795221</v>
       </c>
       <c r="P18">
-        <v>64.38933038907844</v>
+        <v>63.89219478839584</v>
       </c>
       <c r="Q18">
-        <v>161.4893303890784</v>
+        <v>160.9921947883958</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07959696797727313</v>
+        <v>0.07995159249313183</v>
       </c>
       <c r="T18">
-        <v>0.619003337508661</v>
+        <v>0.625498410055599</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.095041159377322</v>
+        <v>8.560038738237481</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07409057176929941</v>
+        <v>0.07404369043768941</v>
       </c>
       <c r="C19">
-        <v>921.3979220825995</v>
+        <v>911.1855521678482</v>
       </c>
       <c r="D19">
-        <v>1100.403006449926</v>
+        <v>1101.122700321488</v>
       </c>
       <c r="E19">
-        <v>42.63870573599425</v>
+        <v>53.57076952230759</v>
       </c>
       <c r="F19">
-        <v>185.8450843673265</v>
+        <v>196.7771481536398</v>
       </c>
       <c r="G19">
         <v>6.84</v>
@@ -2845,28 +2845,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M19">
-        <v>9.942712013651967</v>
+        <v>10.52757742621973</v>
       </c>
       <c r="N19">
-        <v>75.16728798634804</v>
+        <v>74.58242257378028</v>
       </c>
       <c r="O19">
-        <v>11.27509319795221</v>
+        <v>11.18736338606704</v>
       </c>
       <c r="P19">
-        <v>63.89219478839584</v>
+        <v>63.39505918771324</v>
       </c>
       <c r="Q19">
-        <v>160.9921947883958</v>
+        <v>160.4950591877132</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07995159249313183</v>
+        <v>0.08031486638742612</v>
       </c>
       <c r="T19">
-        <v>0.625498410055599</v>
+        <v>0.632151899006121</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.560038738237481</v>
+        <v>8.084481030557619</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07404369043768942</v>
+        <v>0.07399680910607942</v>
       </c>
       <c r="C20">
-        <v>911.185552167848</v>
+        <v>900.9741242684258</v>
       </c>
       <c r="D20">
-        <v>1101.122700321488</v>
+        <v>1101.843336208379</v>
       </c>
       <c r="E20">
-        <v>53.57076952230756</v>
+        <v>64.50283330862089</v>
       </c>
       <c r="F20">
-        <v>196.7771481536398</v>
+        <v>207.7092119399531</v>
       </c>
       <c r="G20">
         <v>6.84</v>
@@ -2927,28 +2927,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M20">
-        <v>10.52757742621973</v>
+        <v>11.11244283878749</v>
       </c>
       <c r="N20">
-        <v>74.58242257378029</v>
+        <v>73.99755716121253</v>
       </c>
       <c r="O20">
-        <v>11.18736338606704</v>
+        <v>11.09963357418188</v>
       </c>
       <c r="P20">
-        <v>63.39505918771325</v>
+        <v>62.89792358703065</v>
       </c>
       <c r="Q20">
-        <v>160.4950591877133</v>
+        <v>159.9979235870306</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08031486638742612</v>
+        <v>0.08068711000750545</v>
       </c>
       <c r="T20">
-        <v>0.632151899006121</v>
+        <v>0.6389696716344336</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.084481030557621</v>
+        <v>7.658982028949325</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07399680910607942</v>
+        <v>0.07408592777446942</v>
       </c>
       <c r="C21">
-        <v>900.9741242684258</v>
+        <v>888.6729805425496</v>
       </c>
       <c r="D21">
-        <v>1101.843336208379</v>
+        <v>1100.474256268816</v>
       </c>
       <c r="E21">
-        <v>64.50283330862089</v>
+        <v>75.43489709493423</v>
       </c>
       <c r="F21">
-        <v>207.7092119399531</v>
+        <v>218.6412757262665</v>
       </c>
       <c r="G21">
         <v>6.84</v>
@@ -3009,45 +3009,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M21">
-        <v>11.11244283878749</v>
+        <v>11.87222127193627</v>
       </c>
       <c r="N21">
-        <v>73.99755716121253</v>
+        <v>73.23777872806374</v>
       </c>
       <c r="O21">
-        <v>11.09963357418188</v>
+        <v>10.98566680920956</v>
       </c>
       <c r="P21">
-        <v>62.89792358703065</v>
+        <v>62.25211191885418</v>
       </c>
       <c r="Q21">
-        <v>159.9979235870306</v>
+        <v>159.3521119188542</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08068711000750545</v>
+        <v>0.08106865971808676</v>
       </c>
       <c r="T21">
-        <v>0.6389696716344336</v>
+        <v>0.645957888578454</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.658982028949325</v>
+        <v>7.168835388975126</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07408592777446942</v>
+        <v>0.07404584644285941</v>
       </c>
       <c r="C22">
-        <v>888.6729805425496</v>
+        <v>878.3562424697815</v>
       </c>
       <c r="D22">
-        <v>1100.474256268816</v>
+        <v>1101.089581982361</v>
       </c>
       <c r="E22">
-        <v>75.43489709493423</v>
+        <v>86.36696088124756</v>
       </c>
       <c r="F22">
-        <v>218.6412757262665</v>
+        <v>229.5733395125798</v>
       </c>
       <c r="G22">
         <v>6.84</v>
@@ -3091,28 +3091,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M22">
-        <v>11.87222127193627</v>
+        <v>12.46583233553308</v>
       </c>
       <c r="N22">
-        <v>73.23777872806374</v>
+        <v>72.64416766446693</v>
       </c>
       <c r="O22">
-        <v>10.98566680920956</v>
+        <v>10.89662514967004</v>
       </c>
       <c r="P22">
-        <v>62.25211191885418</v>
+        <v>61.74754251479689</v>
       </c>
       <c r="Q22">
-        <v>159.3521119188542</v>
+        <v>158.8475425147969</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08106865971808676</v>
+        <v>0.0814598689150119</v>
       </c>
       <c r="T22">
-        <v>0.645957888578454</v>
+        <v>0.6531230224071333</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.168835388975126</v>
+        <v>6.827462275214407</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07404584644285939</v>
+        <v>0.0740057651112494</v>
       </c>
       <c r="C23">
-        <v>878.3562424697819</v>
+        <v>868.0401928957351</v>
       </c>
       <c r="D23">
-        <v>1101.089581982362</v>
+        <v>1101.705596194628</v>
       </c>
       <c r="E23">
-        <v>86.36696088124754</v>
+        <v>97.29902466756084</v>
       </c>
       <c r="F23">
-        <v>229.5733395125798</v>
+        <v>240.5054032988931</v>
       </c>
       <c r="G23">
         <v>6.84</v>
@@ -3173,28 +3173,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M23">
-        <v>12.46583233553308</v>
+        <v>13.05944339912989</v>
       </c>
       <c r="N23">
-        <v>72.64416766446693</v>
+        <v>72.05055660087012</v>
       </c>
       <c r="O23">
-        <v>10.89662514967004</v>
+        <v>10.80758349013052</v>
       </c>
       <c r="P23">
-        <v>61.74754251479689</v>
+        <v>61.24297311073961</v>
       </c>
       <c r="Q23">
-        <v>158.8475425147969</v>
+        <v>158.3429731107396</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08145986891501189</v>
+        <v>0.08186110911698641</v>
       </c>
       <c r="T23">
-        <v>0.6531230224071332</v>
+        <v>0.660471877616035</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.827462275214407</v>
+        <v>6.51712308088648</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0740057651112494</v>
+        <v>0.0739656837796394</v>
       </c>
       <c r="C24">
-        <v>868.0401928957351</v>
+        <v>857.7248329766164</v>
       </c>
       <c r="D24">
-        <v>1101.705596194628</v>
+        <v>1102.322300061823</v>
       </c>
       <c r="E24">
-        <v>97.29902466756084</v>
+        <v>108.2310884538742</v>
       </c>
       <c r="F24">
-        <v>240.5054032988931</v>
+        <v>251.4374670852064</v>
       </c>
       <c r="G24">
         <v>6.84</v>
@@ -3255,28 +3255,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M24">
-        <v>13.05944339912989</v>
+        <v>13.65305446272671</v>
       </c>
       <c r="N24">
-        <v>72.05055660087012</v>
+        <v>71.4569455372733</v>
       </c>
       <c r="O24">
-        <v>10.80758349013052</v>
+        <v>10.718541830591</v>
       </c>
       <c r="P24">
-        <v>61.24297311073961</v>
+        <v>60.73840370668231</v>
       </c>
       <c r="Q24">
-        <v>158.3429731107396</v>
+        <v>157.8384037066823</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08186110911698641</v>
+        <v>0.08227277114238882</v>
       </c>
       <c r="T24">
-        <v>0.660471877616035</v>
+        <v>0.668011612181012</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.51712308088648</v>
+        <v>6.233769903456632</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0739656837796394</v>
+        <v>0.07412960244802939</v>
       </c>
       <c r="C25">
-        <v>857.7248329766164</v>
+        <v>844.2750174573323</v>
       </c>
       <c r="D25">
-        <v>1102.322300061823</v>
+        <v>1099.804548328852</v>
       </c>
       <c r="E25">
-        <v>108.2310884538742</v>
+        <v>119.1631522401875</v>
       </c>
       <c r="F25">
-        <v>251.4374670852064</v>
+        <v>262.3695308715198</v>
       </c>
       <c r="G25">
         <v>6.84</v>
@@ -3337,45 +3337,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M25">
-        <v>13.65305446272671</v>
+        <v>14.50903505719504</v>
       </c>
       <c r="N25">
-        <v>71.4569455372733</v>
+        <v>70.60096494280496</v>
       </c>
       <c r="O25">
-        <v>10.718541830591</v>
+        <v>10.59014474142074</v>
       </c>
       <c r="P25">
-        <v>60.73840370668231</v>
+        <v>60.01082020138422</v>
       </c>
       <c r="Q25">
-        <v>157.8384037066823</v>
+        <v>157.1108202013842</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08227277114238882</v>
+        <v>0.08269526637898604</v>
       </c>
       <c r="T25">
-        <v>0.668011612181012</v>
+        <v>0.6757497608134886</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.233769903456632</v>
+        <v>5.86600002443263</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07412960244802939</v>
+        <v>0.07409802111641939</v>
       </c>
       <c r="C26">
-        <v>844.2750174573324</v>
+        <v>833.8271405289324</v>
       </c>
       <c r="D26">
-        <v>1099.804548328852</v>
+        <v>1100.288735186766</v>
       </c>
       <c r="E26">
-        <v>119.1631522401875</v>
+        <v>130.0952160265008</v>
       </c>
       <c r="F26">
-        <v>262.3695308715197</v>
+        <v>273.301594657833</v>
       </c>
       <c r="G26">
         <v>6.84</v>
@@ -3419,28 +3419,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M26">
-        <v>14.50903505719504</v>
+        <v>15.11357818457817</v>
       </c>
       <c r="N26">
-        <v>70.60096494280498</v>
+        <v>69.99642181542184</v>
       </c>
       <c r="O26">
-        <v>10.59014474142075</v>
+        <v>10.49946327231328</v>
       </c>
       <c r="P26">
-        <v>60.01082020138423</v>
+        <v>59.49695854310856</v>
       </c>
       <c r="Q26">
-        <v>157.1108202013842</v>
+        <v>156.5969585431085</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08269526637898604</v>
+        <v>0.08312902815522585</v>
       </c>
       <c r="T26">
-        <v>0.6757497608134886</v>
+        <v>0.6836942600761644</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.866000024432632</v>
+        <v>5.631360023455326</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07409802111641939</v>
+        <v>0.0740664397848094</v>
       </c>
       <c r="C27">
-        <v>833.8271405289324</v>
+        <v>823.3796901129872</v>
       </c>
       <c r="D27">
-        <v>1100.288735186766</v>
+        <v>1100.773348557134</v>
       </c>
       <c r="E27">
-        <v>130.0952160265008</v>
+        <v>141.0272798128142</v>
       </c>
       <c r="F27">
-        <v>273.301594657833</v>
+        <v>284.2336584441464</v>
       </c>
       <c r="G27">
         <v>6.84</v>
@@ -3501,28 +3501,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M27">
-        <v>15.11357818457817</v>
+        <v>15.7181213119613</v>
       </c>
       <c r="N27">
-        <v>69.99642181542184</v>
+        <v>69.39187868803872</v>
       </c>
       <c r="O27">
-        <v>10.49946327231328</v>
+        <v>10.40878180320581</v>
       </c>
       <c r="P27">
-        <v>59.49695854310856</v>
+        <v>58.98309688483291</v>
       </c>
       <c r="Q27">
-        <v>156.5969585431085</v>
+        <v>156.0830968848329</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08312902815522585</v>
+        <v>0.08357451322271539</v>
       </c>
       <c r="T27">
-        <v>0.6836942600761644</v>
+        <v>0.6918534755351289</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.631360023455326</v>
+        <v>5.414769253322429</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0740664397848094</v>
+        <v>0.07403485845319938</v>
       </c>
       <c r="C28">
-        <v>823.3796901129872</v>
+        <v>812.9326667733085</v>
       </c>
       <c r="D28">
-        <v>1100.773348557134</v>
+        <v>1101.258389003768</v>
       </c>
       <c r="E28">
-        <v>141.0272798128142</v>
+        <v>151.9593435991275</v>
       </c>
       <c r="F28">
-        <v>284.2336584441464</v>
+        <v>295.1657222304597</v>
       </c>
       <c r="G28">
         <v>6.84</v>
@@ -3583,28 +3583,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M28">
-        <v>15.7181213119613</v>
+        <v>16.32266443934442</v>
       </c>
       <c r="N28">
-        <v>69.39187868803872</v>
+        <v>68.78733556065559</v>
       </c>
       <c r="O28">
-        <v>10.40878180320581</v>
+        <v>10.31810033409834</v>
       </c>
       <c r="P28">
-        <v>58.98309688483291</v>
+        <v>58.46923522655725</v>
       </c>
       <c r="Q28">
-        <v>156.0830968848329</v>
+        <v>155.5692352265573</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08357451322271539</v>
+        <v>0.08403220336054709</v>
       </c>
       <c r="T28">
-        <v>0.6918534755351289</v>
+        <v>0.700236231143654</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.414769253322429</v>
+        <v>5.214222243940116</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07403485845319938</v>
+        <v>0.07400327712158938</v>
       </c>
       <c r="C29">
-        <v>812.9326667733085</v>
+        <v>802.4860710746997</v>
       </c>
       <c r="D29">
-        <v>1101.258389003768</v>
+        <v>1101.743857091473</v>
       </c>
       <c r="E29">
-        <v>151.9593435991275</v>
+        <v>162.8914073854408</v>
       </c>
       <c r="F29">
-        <v>295.1657222304597</v>
+        <v>306.0977860167731</v>
       </c>
       <c r="G29">
         <v>6.84</v>
@@ -3665,28 +3665,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M29">
-        <v>16.32266443934442</v>
+        <v>16.92720756672755</v>
       </c>
       <c r="N29">
-        <v>68.78733556065559</v>
+        <v>68.18279243327247</v>
       </c>
       <c r="O29">
-        <v>10.31810033409834</v>
+        <v>10.22741886499087</v>
       </c>
       <c r="P29">
-        <v>58.46923522655725</v>
+        <v>57.9553735682816</v>
       </c>
       <c r="Q29">
-        <v>155.5692352265573</v>
+        <v>155.0553735682816</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08403220336054709</v>
+        <v>0.08450260711331858</v>
       </c>
       <c r="T29">
-        <v>0.700236231143654</v>
+        <v>0.7088518410746382</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.214222243940116</v>
+        <v>5.028000020942256</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07400327712158938</v>
+        <v>0.07397169578997936</v>
       </c>
       <c r="C30">
-        <v>802.4860710746997</v>
+        <v>792.0399035829626</v>
       </c>
       <c r="D30">
-        <v>1101.743857091473</v>
+        <v>1102.229753386049</v>
       </c>
       <c r="E30">
-        <v>162.8914073854408</v>
+        <v>173.8234711717542</v>
       </c>
       <c r="F30">
-        <v>306.0977860167731</v>
+        <v>317.0298498030864</v>
       </c>
       <c r="G30">
         <v>6.84</v>
@@ -3747,28 +3747,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M30">
-        <v>16.92720756672755</v>
+        <v>17.53175069411068</v>
       </c>
       <c r="N30">
-        <v>68.18279243327247</v>
+        <v>67.57824930588933</v>
       </c>
       <c r="O30">
-        <v>10.22741886499087</v>
+        <v>10.1367373958834</v>
       </c>
       <c r="P30">
-        <v>57.9553735682816</v>
+        <v>57.44151191000593</v>
       </c>
       <c r="Q30">
-        <v>155.0553735682816</v>
+        <v>154.5415119100059</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08450260711331858</v>
+        <v>0.08498626167602728</v>
       </c>
       <c r="T30">
-        <v>0.7088518410746382</v>
+        <v>0.7177101442431147</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.028000020942256</v>
+        <v>4.85462070987528</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07397169578997936</v>
+        <v>0.07394011445836936</v>
       </c>
       <c r="C31">
-        <v>792.0399035829626</v>
+        <v>781.5941648648957</v>
       </c>
       <c r="D31">
-        <v>1102.229753386049</v>
+        <v>1102.716078454295</v>
       </c>
       <c r="E31">
-        <v>173.8234711717541</v>
+        <v>184.7555349580674</v>
       </c>
       <c r="F31">
-        <v>317.0298498030863</v>
+        <v>327.9619135893997</v>
       </c>
       <c r="G31">
         <v>6.84</v>
@@ -3829,28 +3829,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M31">
-        <v>17.53175069411067</v>
+        <v>18.1362938214938</v>
       </c>
       <c r="N31">
-        <v>67.57824930588934</v>
+        <v>66.97370617850621</v>
       </c>
       <c r="O31">
-        <v>10.1367373958834</v>
+        <v>10.04605592677593</v>
       </c>
       <c r="P31">
-        <v>57.44151191000594</v>
+        <v>56.92765025173028</v>
       </c>
       <c r="Q31">
-        <v>154.5415119100059</v>
+        <v>154.0276502517303</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08498626167602728</v>
+        <v>0.08548373494052766</v>
       </c>
       <c r="T31">
-        <v>0.7177101442431147</v>
+        <v>0.7268215417878334</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.854620709875281</v>
+        <v>4.692800019546105</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07394011445836936</v>
+        <v>0.07390853312675935</v>
       </c>
       <c r="C32">
-        <v>781.5941648648957</v>
+        <v>771.1488554882998</v>
       </c>
       <c r="D32">
-        <v>1102.716078454295</v>
+        <v>1103.202832864013</v>
       </c>
       <c r="E32">
-        <v>184.7555349580674</v>
+        <v>195.6875987443808</v>
       </c>
       <c r="F32">
-        <v>327.9619135893997</v>
+        <v>338.893977375713</v>
       </c>
       <c r="G32">
         <v>6.84</v>
@@ -3911,28 +3911,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M32">
-        <v>18.1362938214938</v>
+        <v>18.74083694887693</v>
       </c>
       <c r="N32">
-        <v>66.97370617850621</v>
+        <v>66.36916305112308</v>
       </c>
       <c r="O32">
-        <v>10.04605592677593</v>
+        <v>9.955374457668462</v>
       </c>
       <c r="P32">
-        <v>56.92765025173028</v>
+        <v>56.41378859345462</v>
       </c>
       <c r="Q32">
-        <v>154.0276502517303</v>
+        <v>153.5137885934546</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08548373494052766</v>
+        <v>0.0859956277199411</v>
       </c>
       <c r="T32">
-        <v>0.7268215417878334</v>
+        <v>0.7361970378121093</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.692800019546105</v>
+        <v>4.541419373754294</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07390853312675935</v>
+        <v>0.07455695179514935</v>
       </c>
       <c r="C33">
-        <v>771.1488554882998</v>
+        <v>750.3082816849205</v>
       </c>
       <c r="D33">
-        <v>1103.202832864013</v>
+        <v>1093.294322846947</v>
       </c>
       <c r="E33">
-        <v>195.6875987443808</v>
+        <v>206.6196625306941</v>
       </c>
       <c r="F33">
-        <v>338.893977375713</v>
+        <v>349.8260411620263</v>
       </c>
       <c r="G33">
         <v>6.84</v>
@@ -3993,45 +3993,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M33">
-        <v>18.74083694887693</v>
+        <v>20.21994517916512</v>
       </c>
       <c r="N33">
-        <v>66.36916305112308</v>
+        <v>64.89005482083489</v>
       </c>
       <c r="O33">
-        <v>9.955374457668462</v>
+        <v>9.733508223125233</v>
       </c>
       <c r="P33">
-        <v>56.41378859345462</v>
+        <v>55.15654659770966</v>
       </c>
       <c r="Q33">
-        <v>153.5137885934546</v>
+        <v>152.2565465977096</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0859956277199411</v>
+        <v>0.08652257616933728</v>
       </c>
       <c r="T33">
-        <v>0.7361970378121093</v>
+        <v>0.7458482837194521</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.541419373754294</v>
+        <v>4.209210225144349</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07455695179514935</v>
+        <v>0.07454662046353935</v>
       </c>
       <c r="C34">
-        <v>750.3082816849205</v>
+        <v>739.5326958035985</v>
       </c>
       <c r="D34">
-        <v>1093.294322846947</v>
+        <v>1093.450800751938</v>
       </c>
       <c r="E34">
-        <v>206.6196625306941</v>
+        <v>217.5517263170074</v>
       </c>
       <c r="F34">
-        <v>349.8260411620263</v>
+        <v>360.7581049483396</v>
       </c>
       <c r="G34">
         <v>6.84</v>
@@ -4075,28 +4075,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M34">
-        <v>20.21994517916512</v>
+        <v>20.85181846601403</v>
       </c>
       <c r="N34">
-        <v>64.89005482083489</v>
+        <v>64.25818153398598</v>
       </c>
       <c r="O34">
-        <v>9.733508223125233</v>
+        <v>9.638727230097896</v>
       </c>
       <c r="P34">
-        <v>55.15654659770966</v>
+        <v>54.61945430388808</v>
       </c>
       <c r="Q34">
-        <v>152.2565465977096</v>
+        <v>151.7194543038881</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08652257616933728</v>
+        <v>0.08706525442319307</v>
       </c>
       <c r="T34">
-        <v>0.7458482837194521</v>
+        <v>0.7557876265195514</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.209210225144349</v>
+        <v>4.081658400139974</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07454662046353935</v>
+        <v>0.07554778913192933</v>
       </c>
       <c r="C35">
-        <v>739.5326958035985</v>
+        <v>713.6422719267667</v>
       </c>
       <c r="D35">
-        <v>1093.450800751938</v>
+        <v>1078.49244066142</v>
       </c>
       <c r="E35">
-        <v>217.5517263170074</v>
+        <v>228.4837901033207</v>
       </c>
       <c r="F35">
-        <v>360.7581049483396</v>
+        <v>371.690168734653</v>
       </c>
       <c r="G35">
         <v>6.84</v>
@@ -4157,45 +4157,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M35">
-        <v>20.85181846601403</v>
+        <v>22.78460734343423</v>
       </c>
       <c r="N35">
-        <v>64.25818153398598</v>
+        <v>62.32539265656578</v>
       </c>
       <c r="O35">
-        <v>9.638727230097896</v>
+        <v>9.348808898484867</v>
       </c>
       <c r="P35">
-        <v>54.61945430388808</v>
+        <v>52.97658375808091</v>
       </c>
       <c r="Q35">
-        <v>151.7194543038881</v>
+        <v>150.0765837580809</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08706525442319307</v>
+        <v>0.08762437747262022</v>
       </c>
       <c r="T35">
-        <v>0.7557876265195514</v>
+        <v>0.7660281615257144</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.15</v>
       </c>
       <c r="W35">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.081658400139974</v>
+        <v>3.735416578268394</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07554778913192933</v>
+        <v>0.07556720780031934</v>
       </c>
       <c r="C36">
-        <v>713.6422719267667</v>
+        <v>702.4241206824843</v>
       </c>
       <c r="D36">
-        <v>1078.49244066142</v>
+        <v>1078.206353203451</v>
       </c>
       <c r="E36">
-        <v>228.4837901033207</v>
+        <v>239.4158538896341</v>
       </c>
       <c r="F36">
-        <v>371.690168734653</v>
+        <v>382.6222325209663</v>
       </c>
       <c r="G36">
         <v>6.84</v>
@@ -4239,28 +4239,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M36">
-        <v>22.78460734343423</v>
+        <v>23.45474285353523</v>
       </c>
       <c r="N36">
-        <v>62.32539265656578</v>
+        <v>61.65525714646478</v>
       </c>
       <c r="O36">
-        <v>9.348808898484867</v>
+        <v>9.248288571969717</v>
       </c>
       <c r="P36">
-        <v>52.97658375808091</v>
+        <v>52.40696857449506</v>
       </c>
       <c r="Q36">
-        <v>150.0765837580809</v>
+        <v>149.5069685744951</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08762437747262022</v>
+        <v>0.08820070430818361</v>
       </c>
       <c r="T36">
-        <v>0.7660281615257144</v>
+        <v>0.7765837899166824</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.735416578268394</v>
+        <v>3.628690390317869</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07556720780031934</v>
+        <v>0.07558662646870934</v>
       </c>
       <c r="C37">
-        <v>702.4241206824843</v>
+        <v>691.2061211765458</v>
       </c>
       <c r="D37">
-        <v>1078.206353203451</v>
+        <v>1077.920417483826</v>
       </c>
       <c r="E37">
-        <v>239.4158538896341</v>
+        <v>250.3479176759474</v>
       </c>
       <c r="F37">
-        <v>382.6222325209663</v>
+        <v>393.5542963072796</v>
       </c>
       <c r="G37">
         <v>6.84</v>
@@ -4321,28 +4321,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M37">
-        <v>23.45474285353523</v>
+        <v>24.12487836363624</v>
       </c>
       <c r="N37">
-        <v>61.65525714646478</v>
+        <v>60.98512163636377</v>
       </c>
       <c r="O37">
-        <v>9.248288571969717</v>
+        <v>9.147768245454566</v>
       </c>
       <c r="P37">
-        <v>52.40696857449506</v>
+        <v>51.83735339090921</v>
       </c>
       <c r="Q37">
-        <v>149.5069685744951</v>
+        <v>148.9373533909092</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08820070430818361</v>
+        <v>0.08879504135735836</v>
       </c>
       <c r="T37">
-        <v>0.7765837899166824</v>
+        <v>0.7874692816948681</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.628690390317869</v>
+        <v>3.527893435031261</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07558662646870934</v>
+        <v>0.07648664513709934</v>
       </c>
       <c r="C38">
-        <v>691.2061211765458</v>
+        <v>667.1858616387359</v>
       </c>
       <c r="D38">
-        <v>1077.920417483826</v>
+        <v>1064.832221732329</v>
       </c>
       <c r="E38">
-        <v>250.3479176759473</v>
+        <v>261.2799814622607</v>
       </c>
       <c r="F38">
-        <v>393.5542963072796</v>
+        <v>404.4863600935929</v>
       </c>
       <c r="G38">
         <v>6.84</v>
@@ -4403,45 +4403,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M38">
-        <v>24.12487836363624</v>
+        <v>25.92757568199931</v>
       </c>
       <c r="N38">
-        <v>60.98512163636377</v>
+        <v>59.18242431800071</v>
       </c>
       <c r="O38">
-        <v>9.147768245454566</v>
+        <v>8.877363647700106</v>
       </c>
       <c r="P38">
-        <v>51.83735339090921</v>
+        <v>50.3050606703006</v>
       </c>
       <c r="Q38">
-        <v>148.9373533909092</v>
+        <v>147.4050606703006</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08879504135735834</v>
+        <v>0.08940824624936403</v>
       </c>
       <c r="T38">
-        <v>0.787469281694868</v>
+        <v>0.7987003446406151</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.527893435031261</v>
+        <v>3.282605402212332</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07648664513709934</v>
+        <v>0.07652986380548933</v>
       </c>
       <c r="C39">
-        <v>667.1858616387359</v>
+        <v>655.6332989949483</v>
       </c>
       <c r="D39">
-        <v>1064.832221732329</v>
+        <v>1064.211722874855</v>
       </c>
       <c r="E39">
-        <v>261.2799814622607</v>
+        <v>272.212045248574</v>
       </c>
       <c r="F39">
-        <v>404.4863600935929</v>
+        <v>415.4184238799062</v>
       </c>
       <c r="G39">
         <v>6.84</v>
@@ -4485,28 +4485,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M39">
-        <v>25.92757568199931</v>
+        <v>26.62832097070199</v>
       </c>
       <c r="N39">
-        <v>59.18242431800071</v>
+        <v>58.48167902929802</v>
       </c>
       <c r="O39">
-        <v>8.877363647700106</v>
+        <v>8.772251854394703</v>
       </c>
       <c r="P39">
-        <v>50.3050606703006</v>
+        <v>49.70942717490332</v>
       </c>
       <c r="Q39">
-        <v>147.4050606703006</v>
+        <v>146.8094271749033</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08940824624936403</v>
+        <v>0.09004123194433764</v>
       </c>
       <c r="T39">
-        <v>0.7987003446406151</v>
+        <v>0.8102936999394509</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.282605402212332</v>
+        <v>3.196221049522534</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07652986380548933</v>
+        <v>0.07657308247387934</v>
       </c>
       <c r="C40">
-        <v>655.6332989949483</v>
+        <v>644.0814590839946</v>
       </c>
       <c r="D40">
-        <v>1064.211722874855</v>
+        <v>1063.591946750214</v>
       </c>
       <c r="E40">
-        <v>272.212045248574</v>
+        <v>283.1441090348874</v>
       </c>
       <c r="F40">
-        <v>415.4184238799062</v>
+        <v>426.3504876662196</v>
       </c>
       <c r="G40">
         <v>6.84</v>
@@ -4567,28 +4567,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M40">
-        <v>26.62832097070199</v>
+        <v>27.32906625940468</v>
       </c>
       <c r="N40">
-        <v>58.48167902929802</v>
+        <v>57.78093374059534</v>
       </c>
       <c r="O40">
-        <v>8.772251854394703</v>
+        <v>8.667140061089301</v>
       </c>
       <c r="P40">
-        <v>49.70942717490332</v>
+        <v>49.11379367950604</v>
       </c>
       <c r="Q40">
-        <v>146.8094271749033</v>
+        <v>146.213793679506</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09004123194433764</v>
+        <v>0.09069497126865464</v>
       </c>
       <c r="T40">
-        <v>0.8102936999394509</v>
+        <v>0.8222671652480845</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.196221049522534</v>
+        <v>3.11426666363734</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07657308247387934</v>
+        <v>0.07661630114226933</v>
       </c>
       <c r="C41">
-        <v>644.0814590839946</v>
+        <v>632.5303406438934</v>
       </c>
       <c r="D41">
-        <v>1063.591946750214</v>
+        <v>1062.972892096426</v>
       </c>
       <c r="E41">
-        <v>283.1441090348874</v>
+        <v>294.0761728212007</v>
       </c>
       <c r="F41">
-        <v>426.3504876662196</v>
+        <v>437.2825514525329</v>
       </c>
       <c r="G41">
         <v>6.84</v>
@@ -4649,28 +4649,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M41">
-        <v>27.32906625940468</v>
+        <v>28.02981154810736</v>
       </c>
       <c r="N41">
-        <v>57.78093374059534</v>
+        <v>57.08018845189265</v>
       </c>
       <c r="O41">
-        <v>8.667140061089301</v>
+        <v>8.562028267783898</v>
       </c>
       <c r="P41">
-        <v>49.11379367950604</v>
+        <v>48.51816018410875</v>
       </c>
       <c r="Q41">
-        <v>146.213793679506</v>
+        <v>145.6181601841087</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09069497126865464</v>
+        <v>0.09137050190378221</v>
       </c>
       <c r="T41">
-        <v>0.8222671652480845</v>
+        <v>0.8346397460670061</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.11426666363734</v>
+        <v>3.036409997046407</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07661630114226933</v>
+        <v>0.07937781981065932</v>
       </c>
       <c r="C42">
-        <v>632.5303406438934</v>
+        <v>583.4834223993824</v>
       </c>
       <c r="D42">
-        <v>1062.972892096426</v>
+        <v>1024.858037638229</v>
       </c>
       <c r="E42">
-        <v>294.0761728212007</v>
+        <v>305.008236607514</v>
       </c>
       <c r="F42">
-        <v>437.2825514525329</v>
+        <v>448.2146152388462</v>
       </c>
       <c r="G42">
         <v>6.84</v>
@@ -4731,45 +4731,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M42">
-        <v>28.02981154810736</v>
+        <v>32.22663083567305</v>
       </c>
       <c r="N42">
-        <v>57.08018845189265</v>
+        <v>52.88336916432696</v>
       </c>
       <c r="O42">
-        <v>8.562028267783898</v>
+        <v>7.932505374649044</v>
       </c>
       <c r="P42">
-        <v>48.51816018410875</v>
+        <v>44.95086378967792</v>
       </c>
       <c r="Q42">
-        <v>145.6181601841087</v>
+        <v>142.0508637896779</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09137050190378221</v>
+        <v>0.09206893188247342</v>
       </c>
       <c r="T42">
-        <v>0.8346397460670061</v>
+        <v>0.8474317364052129</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.036409997046407</v>
+        <v>2.640983490765286</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07937781981065932</v>
+        <v>0.07948733847904932</v>
       </c>
       <c r="C43">
-        <v>583.4834223993824</v>
+        <v>571.0960375563359</v>
       </c>
       <c r="D43">
-        <v>1024.858037638229</v>
+        <v>1023.402716581495</v>
       </c>
       <c r="E43">
-        <v>305.008236607514</v>
+        <v>315.9403003938273</v>
       </c>
       <c r="F43">
-        <v>448.2146152388462</v>
+        <v>459.1466790251596</v>
       </c>
       <c r="G43">
         <v>6.84</v>
@@ -4813,28 +4813,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M43">
-        <v>32.22663083567305</v>
+        <v>33.01264622190898</v>
       </c>
       <c r="N43">
-        <v>52.88336916432696</v>
+        <v>52.09735377809103</v>
       </c>
       <c r="O43">
-        <v>7.932505374649044</v>
+        <v>7.814603066713655</v>
       </c>
       <c r="P43">
-        <v>44.95086378967792</v>
+        <v>44.28275071137737</v>
       </c>
       <c r="Q43">
-        <v>142.0508637896779</v>
+        <v>141.3827507113774</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09206893188247342</v>
+        <v>0.09279144565353331</v>
       </c>
       <c r="T43">
-        <v>0.8474317364052129</v>
+        <v>0.8606648298585304</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.640983490765286</v>
+        <v>2.57810293146135</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07948733847904932</v>
+        <v>0.0795968571474393</v>
       </c>
       <c r="C44">
-        <v>571.0960375563359</v>
+        <v>558.7127800285195</v>
       </c>
       <c r="D44">
-        <v>1023.402716581495</v>
+        <v>1021.951522839993</v>
       </c>
       <c r="E44">
-        <v>315.9403003938273</v>
+        <v>326.8723641801406</v>
       </c>
       <c r="F44">
-        <v>459.1466790251595</v>
+        <v>470.0787428114729</v>
       </c>
       <c r="G44">
         <v>6.84</v>
@@ -4895,28 +4895,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M44">
-        <v>33.01264622190897</v>
+        <v>33.7986616081449</v>
       </c>
       <c r="N44">
-        <v>52.09735377809104</v>
+        <v>51.31133839185511</v>
       </c>
       <c r="O44">
-        <v>7.814603066713656</v>
+        <v>7.696700758778266</v>
       </c>
       <c r="P44">
-        <v>44.28275071137738</v>
+        <v>43.61463763307685</v>
       </c>
       <c r="Q44">
-        <v>141.3827507113774</v>
+        <v>140.7146376330768</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0927914456535333</v>
+        <v>0.09353931078498123</v>
       </c>
       <c r="T44">
-        <v>0.8606648298585303</v>
+        <v>0.8743622423803853</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.578102931461351</v>
+        <v>2.518147049334343</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0795968571474393</v>
+        <v>0.08116497581582931</v>
       </c>
       <c r="C45">
-        <v>558.7127800285195</v>
+        <v>527.4444814929839</v>
       </c>
       <c r="D45">
-        <v>1021.951522839993</v>
+        <v>1001.61528809077</v>
       </c>
       <c r="E45">
-        <v>326.8723641801406</v>
+        <v>337.8044279664539</v>
       </c>
       <c r="F45">
-        <v>470.0787428114729</v>
+        <v>481.0108065977861</v>
       </c>
       <c r="G45">
         <v>6.84</v>
@@ -4977,45 +4977,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M45">
-        <v>33.7986616081449</v>
+        <v>36.46061914011219</v>
       </c>
       <c r="N45">
-        <v>51.31133839185511</v>
+        <v>48.64938085988782</v>
       </c>
       <c r="O45">
-        <v>7.696700758778266</v>
+        <v>7.297407128983172</v>
       </c>
       <c r="P45">
-        <v>43.61463763307685</v>
+        <v>41.35197373090465</v>
       </c>
       <c r="Q45">
-        <v>140.7146376330768</v>
+        <v>138.4519737309046</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09353931078498123</v>
+        <v>0.09431388538540947</v>
       </c>
       <c r="T45">
-        <v>0.8743622423803853</v>
+        <v>0.8885488482065921</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.518147049334343</v>
+        <v>2.334299362085329</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08116497581582931</v>
+        <v>0.0813076444842193</v>
       </c>
       <c r="C46">
-        <v>527.4444814929839</v>
+        <v>514.702306258956</v>
       </c>
       <c r="D46">
-        <v>1001.61528809077</v>
+        <v>999.8051766430555</v>
       </c>
       <c r="E46">
-        <v>337.8044279664539</v>
+        <v>348.7364917527673</v>
       </c>
       <c r="F46">
-        <v>481.0108065977861</v>
+        <v>491.9428703840995</v>
       </c>
       <c r="G46">
         <v>6.84</v>
@@ -5059,28 +5059,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M46">
-        <v>36.46061914011219</v>
+        <v>37.28926957511474</v>
       </c>
       <c r="N46">
-        <v>48.64938085988782</v>
+        <v>47.82073042488527</v>
       </c>
       <c r="O46">
-        <v>7.297407128983172</v>
+        <v>7.17310956373279</v>
       </c>
       <c r="P46">
-        <v>41.35197373090465</v>
+        <v>40.64762086115248</v>
       </c>
       <c r="Q46">
-        <v>138.4519737309046</v>
+        <v>137.7476208611525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09431388538540947</v>
+        <v>0.09511662633494418</v>
       </c>
       <c r="T46">
-        <v>0.8885488482065921</v>
+        <v>0.9032513306082974</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.334299362085329</v>
+        <v>2.282426042927876</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0813076444842193</v>
+        <v>0.0814503131526093</v>
       </c>
       <c r="C47">
-        <v>514.702306258956</v>
+        <v>501.9666616617939</v>
       </c>
       <c r="D47">
-        <v>999.8051766430555</v>
+        <v>998.0015958322067</v>
       </c>
       <c r="E47">
-        <v>348.7364917527673</v>
+        <v>359.6685555390806</v>
       </c>
       <c r="F47">
-        <v>491.9428703840995</v>
+        <v>502.8749341704128</v>
       </c>
       <c r="G47">
         <v>6.84</v>
@@ -5141,28 +5141,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M47">
-        <v>37.28926957511474</v>
+        <v>38.1179200101173</v>
       </c>
       <c r="N47">
-        <v>47.82073042488527</v>
+        <v>46.99207998988272</v>
       </c>
       <c r="O47">
-        <v>7.17310956373279</v>
+        <v>7.048811998482408</v>
       </c>
       <c r="P47">
-        <v>40.64762086115248</v>
+        <v>39.94326799140031</v>
       </c>
       <c r="Q47">
-        <v>137.7476208611525</v>
+        <v>137.0432679914003</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09511662633494418</v>
+        <v>0.09594909843075795</v>
       </c>
       <c r="T47">
-        <v>0.9032513306082974</v>
+        <v>0.9184983493952512</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.282426042927876</v>
+        <v>2.232808085472923</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0814503131526093</v>
+        <v>0.08159298182099931</v>
       </c>
       <c r="C48">
-        <v>501.9666616617939</v>
+        <v>489.2375124226586</v>
       </c>
       <c r="D48">
-        <v>998.0015958322067</v>
+        <v>996.2045103793847</v>
       </c>
       <c r="E48">
-        <v>359.6685555390806</v>
+        <v>370.600619325394</v>
       </c>
       <c r="F48">
-        <v>502.8749341704128</v>
+        <v>513.8069979567261</v>
       </c>
       <c r="G48">
         <v>6.84</v>
@@ -5223,28 +5223,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M48">
-        <v>38.1179200101173</v>
+        <v>38.94657044511985</v>
       </c>
       <c r="N48">
-        <v>46.99207998988272</v>
+        <v>46.16342955488017</v>
       </c>
       <c r="O48">
-        <v>7.048811998482408</v>
+        <v>6.924514433232025</v>
       </c>
       <c r="P48">
-        <v>39.94326799140031</v>
+        <v>39.23891512164814</v>
       </c>
       <c r="Q48">
-        <v>137.0432679914003</v>
+        <v>136.3389151216481</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09594909843075795</v>
+        <v>0.0968129845679232</v>
       </c>
       <c r="T48">
-        <v>0.9184983493952512</v>
+        <v>0.9343207273817126</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.232808085472923</v>
+        <v>2.185301530462861</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08159298182099931</v>
+        <v>0.08173565048938929</v>
       </c>
       <c r="C49">
-        <v>489.2375124226586</v>
+        <v>476.514823516359</v>
       </c>
       <c r="D49">
-        <v>996.2045103793847</v>
+        <v>994.4138852593985</v>
       </c>
       <c r="E49">
-        <v>370.600619325394</v>
+        <v>381.5326831117073</v>
       </c>
       <c r="F49">
-        <v>513.8069979567261</v>
+        <v>524.7390617430395</v>
       </c>
       <c r="G49">
         <v>6.84</v>
@@ -5305,28 +5305,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M49">
-        <v>38.94657044511985</v>
+        <v>39.7752208801224</v>
       </c>
       <c r="N49">
-        <v>46.16342955488017</v>
+        <v>45.33477911987762</v>
       </c>
       <c r="O49">
-        <v>6.924514433232025</v>
+        <v>6.800216867981642</v>
       </c>
       <c r="P49">
-        <v>39.23891512164814</v>
+        <v>38.53456225189598</v>
       </c>
       <c r="Q49">
-        <v>136.3389151216481</v>
+        <v>135.634562251896</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0968129845679232</v>
+        <v>0.0977100970949794</v>
       </c>
       <c r="T49">
-        <v>0.9343207273817126</v>
+        <v>0.9507516583676532</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.185301530462861</v>
+        <v>2.139774415244884</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08173565048938929</v>
+        <v>0.08187831915777928</v>
       </c>
       <c r="C50">
-        <v>476.5148235163591</v>
+        <v>463.7985601690751</v>
       </c>
       <c r="D50">
-        <v>994.4138852593985</v>
+        <v>992.6296856984279</v>
       </c>
       <c r="E50">
-        <v>381.5326831117072</v>
+        <v>392.4647468980206</v>
       </c>
       <c r="F50">
-        <v>524.7390617430394</v>
+        <v>535.6711255293528</v>
       </c>
       <c r="G50">
         <v>6.84</v>
@@ -5387,28 +5387,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M50">
-        <v>39.77522088012239</v>
+        <v>40.60387131512495</v>
       </c>
       <c r="N50">
-        <v>45.33477911987762</v>
+        <v>44.50612868487507</v>
       </c>
       <c r="O50">
-        <v>6.800216867981644</v>
+        <v>6.67591930273126</v>
       </c>
       <c r="P50">
-        <v>38.53456225189598</v>
+        <v>37.83020938214381</v>
       </c>
       <c r="Q50">
-        <v>135.634562251896</v>
+        <v>134.9302093821438</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0977100970949794</v>
+        <v>0.09864239050544957</v>
       </c>
       <c r="T50">
-        <v>0.9507516583676532</v>
+        <v>0.9678269395883365</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.139774415244885</v>
+        <v>2.096105549627642</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08187831915777928</v>
+        <v>0.08202098782616929</v>
       </c>
       <c r="C51">
-        <v>463.7985601690751</v>
+        <v>451.0886878561082</v>
       </c>
       <c r="D51">
-        <v>992.6296856984279</v>
+        <v>990.8518771717743</v>
       </c>
       <c r="E51">
-        <v>392.4647468980206</v>
+        <v>403.3968106843339</v>
       </c>
       <c r="F51">
-        <v>535.6711255293528</v>
+        <v>546.6031893156661</v>
       </c>
       <c r="G51">
         <v>6.84</v>
@@ -5469,28 +5469,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M51">
-        <v>40.60387131512495</v>
+        <v>41.43252175012749</v>
       </c>
       <c r="N51">
-        <v>44.50612868487507</v>
+        <v>43.67747824987252</v>
       </c>
       <c r="O51">
-        <v>6.67591930273126</v>
+        <v>6.551621737480878</v>
       </c>
       <c r="P51">
-        <v>37.83020938214381</v>
+        <v>37.12585651239164</v>
       </c>
       <c r="Q51">
-        <v>134.9302093821438</v>
+        <v>134.2258565123916</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09864239050544957</v>
+        <v>0.09961197565233856</v>
       </c>
       <c r="T51">
-        <v>0.9678269395883365</v>
+        <v>0.9855852320578475</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.096105549627642</v>
+        <v>2.054183438635089</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08202098782616929</v>
+        <v>0.08216365649455927</v>
       </c>
       <c r="C52">
-        <v>451.0886878561082</v>
+        <v>438.385172299654</v>
       </c>
       <c r="D52">
-        <v>990.8518771717743</v>
+        <v>989.0804254016333</v>
       </c>
       <c r="E52">
-        <v>403.3968106843339</v>
+        <v>414.3288744706472</v>
       </c>
       <c r="F52">
-        <v>546.6031893156661</v>
+        <v>557.5352531019794</v>
       </c>
       <c r="G52">
         <v>6.84</v>
@@ -5551,28 +5551,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M52">
-        <v>41.43252175012749</v>
+        <v>42.26117218513004</v>
       </c>
       <c r="N52">
-        <v>43.67747824987252</v>
+        <v>42.84882781486997</v>
       </c>
       <c r="O52">
-        <v>6.551621737480878</v>
+        <v>6.427324172230495</v>
       </c>
       <c r="P52">
-        <v>37.12585651239164</v>
+        <v>36.42150364263948</v>
       </c>
       <c r="Q52">
-        <v>134.2258565123916</v>
+        <v>133.5215036426395</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09961197565233856</v>
+        <v>0.1006211357031822</v>
       </c>
       <c r="T52">
-        <v>0.9855852320578475</v>
+        <v>1.00406835279142</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.054183438635089</v>
+        <v>2.013905331995185</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08216365649455927</v>
+        <v>0.08858272516294927</v>
       </c>
       <c r="C53">
-        <v>438.385172299654</v>
+        <v>353.8161974722312</v>
       </c>
       <c r="D53">
-        <v>989.0804254016333</v>
+        <v>915.443514360524</v>
       </c>
       <c r="E53">
-        <v>414.3288744706472</v>
+        <v>425.2609382569606</v>
       </c>
       <c r="F53">
-        <v>557.5352531019794</v>
+        <v>568.4673168882928</v>
       </c>
       <c r="G53">
         <v>6.84</v>
@@ -5633,45 +5633,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M53">
-        <v>42.26117218513004</v>
+        <v>51.16205851994635</v>
       </c>
       <c r="N53">
-        <v>42.84882781486997</v>
+        <v>33.94794148005366</v>
       </c>
       <c r="O53">
-        <v>6.427324172230495</v>
+        <v>5.09219122200805</v>
       </c>
       <c r="P53">
-        <v>36.42150364263948</v>
+        <v>28.85575025804561</v>
       </c>
       <c r="Q53">
-        <v>133.5215036426395</v>
+        <v>125.9557502580456</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1006211357031822</v>
+        <v>0.1016723440894776</v>
       </c>
       <c r="T53">
-        <v>1.00406835279142</v>
+        <v>1.023321603555558</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.013905331995185</v>
+        <v>1.663537442826279</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08858272516294927</v>
+        <v>0.08884609383133926</v>
       </c>
       <c r="C54">
-        <v>353.8161974722312</v>
+        <v>340.0963246932423</v>
       </c>
       <c r="D54">
-        <v>915.443514360524</v>
+        <v>912.6557053678483</v>
       </c>
       <c r="E54">
-        <v>425.2609382569606</v>
+        <v>436.1930020432739</v>
       </c>
       <c r="F54">
-        <v>568.4673168882928</v>
+        <v>579.399380674606</v>
       </c>
       <c r="G54">
         <v>6.84</v>
@@ -5715,28 +5715,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M54">
-        <v>51.16205851994635</v>
+        <v>52.14594426071454</v>
       </c>
       <c r="N54">
-        <v>33.94794148005366</v>
+        <v>32.96405573928547</v>
       </c>
       <c r="O54">
-        <v>5.09219122200805</v>
+        <v>4.94460836089282</v>
       </c>
       <c r="P54">
-        <v>28.85575025804561</v>
+        <v>28.01944737839265</v>
       </c>
       <c r="Q54">
-        <v>125.9557502580456</v>
+        <v>125.1194473783926</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1016723440894776</v>
+        <v>0.1027682847475304</v>
       </c>
       <c r="T54">
-        <v>1.023321603555558</v>
+        <v>1.043394141586255</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.663537442826279</v>
+        <v>1.632149943905029</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08884609383133926</v>
+        <v>0.08910946249972926</v>
       </c>
       <c r="C55">
-        <v>340.0963246932423</v>
+        <v>326.3933798468602</v>
       </c>
       <c r="D55">
-        <v>912.6557053678483</v>
+        <v>909.8848243077796</v>
       </c>
       <c r="E55">
-        <v>436.1930020432739</v>
+        <v>447.1250658295872</v>
       </c>
       <c r="F55">
-        <v>579.399380674606</v>
+        <v>590.3314444609194</v>
       </c>
       <c r="G55">
         <v>6.84</v>
@@ -5797,28 +5797,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M55">
-        <v>52.14594426071454</v>
+        <v>53.12983000148274</v>
       </c>
       <c r="N55">
-        <v>32.96405573928547</v>
+        <v>31.98016999851727</v>
       </c>
       <c r="O55">
-        <v>4.94460836089282</v>
+        <v>4.797025499777591</v>
       </c>
       <c r="P55">
-        <v>28.01944737839265</v>
+        <v>27.18314449873968</v>
       </c>
       <c r="Q55">
-        <v>125.1194473783926</v>
+        <v>124.2831444987397</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1027682847475304</v>
+        <v>0.1039118749994114</v>
       </c>
       <c r="T55">
-        <v>1.043394141586255</v>
+        <v>1.064339398661765</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.632149943905029</v>
+        <v>1.601924944943825</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08910946249972926</v>
+        <v>0.08937283116811925</v>
       </c>
       <c r="C56">
-        <v>326.3933798468602</v>
+        <v>312.7072092169208</v>
       </c>
       <c r="D56">
-        <v>909.8848243077796</v>
+        <v>907.1307174641535</v>
       </c>
       <c r="E56">
-        <v>447.1250658295872</v>
+        <v>458.0571296159005</v>
       </c>
       <c r="F56">
-        <v>590.3314444609194</v>
+        <v>601.2635082472327</v>
       </c>
       <c r="G56">
         <v>6.84</v>
@@ -5879,28 +5879,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M56">
-        <v>53.12983000148274</v>
+        <v>54.11371574225095</v>
       </c>
       <c r="N56">
-        <v>31.98016999851727</v>
+        <v>30.99628425774907</v>
       </c>
       <c r="O56">
-        <v>4.797025499777591</v>
+        <v>4.64944263866236</v>
       </c>
       <c r="P56">
-        <v>27.18314449873968</v>
+        <v>26.34684161908671</v>
       </c>
       <c r="Q56">
-        <v>124.2831444987397</v>
+        <v>123.4468416190867</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1039118749994114</v>
+        <v>0.1051062914847095</v>
       </c>
       <c r="T56">
-        <v>1.064339398661765</v>
+        <v>1.086215556051742</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.601924944943825</v>
+        <v>1.572799036853937</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08937283116811925</v>
+        <v>0.08963619983650925</v>
       </c>
       <c r="C57">
-        <v>312.7072092169208</v>
+        <v>299.0376609427611</v>
       </c>
       <c r="D57">
-        <v>907.1307174641535</v>
+        <v>904.3932329763072</v>
       </c>
       <c r="E57">
-        <v>458.0571296159005</v>
+        <v>468.9891934022139</v>
       </c>
       <c r="F57">
-        <v>601.2635082472327</v>
+        <v>612.1955720335461</v>
       </c>
       <c r="G57">
         <v>6.84</v>
@@ -5961,28 +5961,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M57">
-        <v>54.11371574225095</v>
+        <v>55.09760148301915</v>
       </c>
       <c r="N57">
-        <v>30.99628425774907</v>
+        <v>30.01239851698087</v>
       </c>
       <c r="O57">
-        <v>4.64944263866236</v>
+        <v>4.501859777547129</v>
       </c>
       <c r="P57">
-        <v>26.34684161908671</v>
+        <v>25.51053873943374</v>
       </c>
       <c r="Q57">
-        <v>123.4468416190867</v>
+        <v>122.6105387394337</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1051062914847095</v>
+        <v>0.1063549996284301</v>
       </c>
       <c r="T57">
-        <v>1.086215556051742</v>
+        <v>1.109086084232172</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.572799036853937</v>
+        <v>1.544713339767259</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08963619983650925</v>
+        <v>0.08989956850489925</v>
       </c>
       <c r="C58">
-        <v>299.0376609427611</v>
+        <v>285.3845849913077</v>
       </c>
       <c r="D58">
-        <v>904.3932329763072</v>
+        <v>901.6722208111671</v>
       </c>
       <c r="E58">
-        <v>468.9891934022139</v>
+        <v>479.9212571885272</v>
       </c>
       <c r="F58">
-        <v>612.1955720335461</v>
+        <v>623.1276358198594</v>
       </c>
       <c r="G58">
         <v>6.84</v>
@@ -6043,28 +6043,28 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M58">
-        <v>55.09760148301915</v>
+        <v>56.08148722378734</v>
       </c>
       <c r="N58">
-        <v>30.01239851698087</v>
+        <v>29.02851277621267</v>
       </c>
       <c r="O58">
-        <v>4.501859777547129</v>
+        <v>4.354276916431901</v>
       </c>
       <c r="P58">
-        <v>25.51053873943374</v>
+        <v>24.67423585978077</v>
       </c>
       <c r="Q58">
-        <v>122.6105387394337</v>
+        <v>121.7742358597808</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1063549996284301</v>
+        <v>0.1076617872206959</v>
       </c>
       <c r="T58">
-        <v>1.109086084232172</v>
+        <v>1.133020357909367</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.544713339767259</v>
+        <v>1.517613105736255</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08989956850489925</v>
+        <v>0.1194755882075678</v>
       </c>
       <c r="C59">
-        <v>285.3845849913077</v>
+        <v>46.74164032951558</v>
       </c>
       <c r="D59">
-        <v>901.6722208111671</v>
+        <v>673.9613399356883</v>
       </c>
       <c r="E59">
-        <v>479.9212571885272</v>
+        <v>490.8533209748406</v>
       </c>
       <c r="F59">
-        <v>623.1276358198594</v>
+        <v>634.0596996061728</v>
       </c>
       <c r="G59">
         <v>6.84</v>
@@ -6125,45 +6125,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M59">
-        <v>56.08148722378734</v>
+        <v>93.07996390218618</v>
       </c>
       <c r="N59">
-        <v>29.02851277621267</v>
+        <v>-7.969963902186166</v>
       </c>
       <c r="O59">
-        <v>4.354276916431901</v>
+        <v>-1.195494585327925</v>
       </c>
       <c r="P59">
-        <v>24.67423585978077</v>
+        <v>-6.774469316858241</v>
       </c>
       <c r="Q59">
-        <v>121.7742358597808</v>
+        <v>90.32553068314175</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1076617872206959</v>
+        <v>0.109546716800496</v>
       </c>
       <c r="T59">
-        <v>1.133020357909367</v>
+        <v>1.167543505123331</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.15</v>
+        <v>0.1371562629033223</v>
       </c>
       <c r="W59">
-        <v>0.0765</v>
+        <v>0.1266654606057923</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.517613105736255</v>
+        <v>0.914375086022149</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1194755882075678</v>
+        <v>0.1204855882075678</v>
       </c>
       <c r="C60">
-        <v>46.74164032951592</v>
+        <v>30.04692500337035</v>
       </c>
       <c r="D60">
-        <v>673.9613399356886</v>
+        <v>668.1986883958563</v>
       </c>
       <c r="E60">
-        <v>490.8533209748405</v>
+        <v>501.7853847611538</v>
       </c>
       <c r="F60">
-        <v>634.0596996061727</v>
+        <v>644.991763392486</v>
       </c>
       <c r="G60">
         <v>6.84</v>
@@ -6207,37 +6207,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M60">
-        <v>93.07996390218615</v>
+        <v>94.68479086601694</v>
       </c>
       <c r="N60">
-        <v>-7.969963902186137</v>
+        <v>-9.574790866016926</v>
       </c>
       <c r="O60">
-        <v>-1.195494585327921</v>
+        <v>-1.436218629902539</v>
       </c>
       <c r="P60">
-        <v>-6.774469316858217</v>
+        <v>-8.138572236114387</v>
       </c>
       <c r="Q60">
-        <v>90.32553068314178</v>
+        <v>88.96142776388561</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1095467168004959</v>
+        <v>0.1111015147712398</v>
       </c>
       <c r="T60">
-        <v>1.16754350512333</v>
+        <v>1.196020175979997</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1371562629033224</v>
+        <v>0.1348315804812322</v>
       </c>
       <c r="W60">
-        <v>0.1266654606057923</v>
+        <v>0.1270067239853551</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9143750860221493</v>
+        <v>0.8988772032082146</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1204855882075678</v>
+        <v>0.1214955882075678</v>
       </c>
       <c r="C61">
-        <v>30.04692500337035</v>
+        <v>13.44992037505506</v>
       </c>
       <c r="D61">
-        <v>668.1986883958563</v>
+        <v>662.5337475538544</v>
       </c>
       <c r="E61">
-        <v>501.7853847611538</v>
+        <v>512.7174485474671</v>
       </c>
       <c r="F61">
-        <v>644.991763392486</v>
+        <v>655.9238271787993</v>
       </c>
       <c r="G61">
         <v>6.84</v>
@@ -6289,37 +6289,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M61">
-        <v>94.68479086601694</v>
+        <v>96.28961782984776</v>
       </c>
       <c r="N61">
-        <v>-9.574790866016926</v>
+        <v>-11.17961782984774</v>
       </c>
       <c r="O61">
-        <v>-1.436218629902539</v>
+        <v>-1.676942674477161</v>
       </c>
       <c r="P61">
-        <v>-8.138572236114387</v>
+        <v>-9.502675155370582</v>
       </c>
       <c r="Q61">
-        <v>88.96142776388561</v>
+        <v>87.59732484462941</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1111015147712398</v>
+        <v>0.1127340526405207</v>
       </c>
       <c r="T61">
-        <v>1.196020175979997</v>
+        <v>1.225920680379497</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1348315804812322</v>
+        <v>0.1325843874732116</v>
       </c>
       <c r="W61">
-        <v>0.1270067239853551</v>
+        <v>0.1273366119189325</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8988772032082146</v>
+        <v>0.8838959164880775</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1214955882075678</v>
+        <v>0.1225055882075678</v>
       </c>
       <c r="C62">
-        <v>13.44992037505506</v>
+        <v>-3.051837816589682</v>
       </c>
       <c r="D62">
-        <v>662.5337475538544</v>
+        <v>656.9640531485229</v>
       </c>
       <c r="E62">
-        <v>512.7174485474671</v>
+        <v>523.6495123337804</v>
       </c>
       <c r="F62">
-        <v>655.9238271787993</v>
+        <v>666.8558909651126</v>
       </c>
       <c r="G62">
         <v>6.84</v>
@@ -6371,37 +6371,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M62">
-        <v>96.28961782984776</v>
+        <v>97.89444479367855</v>
       </c>
       <c r="N62">
-        <v>-11.17961782984774</v>
+        <v>-12.78444479367853</v>
       </c>
       <c r="O62">
-        <v>-1.676942674477161</v>
+        <v>-1.91766671905178</v>
       </c>
       <c r="P62">
-        <v>-9.502675155370582</v>
+        <v>-10.86677807462675</v>
       </c>
       <c r="Q62">
-        <v>87.59732484462941</v>
+        <v>86.23322192537324</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1127340526405207</v>
+        <v>0.1144503104005341</v>
       </c>
       <c r="T62">
-        <v>1.225920680379497</v>
+        <v>1.257354543978971</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1325843874732116</v>
+        <v>0.1304108729244705</v>
       </c>
       <c r="W62">
-        <v>0.1273366119189325</v>
+        <v>0.1276556838546878</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8838959164880775</v>
+        <v>0.8694058194964698</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1225055882075678</v>
+        <v>0.1235155882075678</v>
       </c>
       <c r="C63">
-        <v>-3.051837816589682</v>
+        <v>-19.46073165873258</v>
       </c>
       <c r="D63">
-        <v>656.9640531485229</v>
+        <v>651.4872230926934</v>
       </c>
       <c r="E63">
-        <v>523.6495123337804</v>
+        <v>534.5815761200938</v>
       </c>
       <c r="F63">
-        <v>666.8558909651126</v>
+        <v>677.787954751426</v>
       </c>
       <c r="G63">
         <v>6.84</v>
@@ -6453,37 +6453,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M63">
-        <v>97.89444479367855</v>
+        <v>99.49927175750935</v>
       </c>
       <c r="N63">
-        <v>-12.78444479367853</v>
+        <v>-14.38927175750933</v>
       </c>
       <c r="O63">
-        <v>-1.91766671905178</v>
+        <v>-2.1583907636264</v>
       </c>
       <c r="P63">
-        <v>-10.86677807462675</v>
+        <v>-12.23088099388293</v>
       </c>
       <c r="Q63">
-        <v>86.23322192537324</v>
+        <v>84.86911900611706</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1144503104005341</v>
+        <v>0.1162568975163376</v>
       </c>
       <c r="T63">
-        <v>1.257354543978971</v>
+        <v>1.290442821452102</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1304108729244705</v>
+        <v>0.1283074717482693</v>
       </c>
       <c r="W63">
-        <v>0.1276556838546878</v>
+        <v>0.1279644631473541</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8694058194964698</v>
+        <v>0.8553831449884621</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1235155882075678</v>
+        <v>0.1245255882075678</v>
       </c>
       <c r="C64">
-        <v>-19.46073165873258</v>
+        <v>-35.77906446148006</v>
       </c>
       <c r="D64">
-        <v>651.4872230926934</v>
+        <v>646.1009540762592</v>
       </c>
       <c r="E64">
-        <v>534.5815761200938</v>
+        <v>545.5136399064071</v>
       </c>
       <c r="F64">
-        <v>677.787954751426</v>
+        <v>688.7200185377393</v>
       </c>
       <c r="G64">
         <v>6.84</v>
@@ -6535,37 +6535,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M64">
-        <v>99.49927175750935</v>
+        <v>101.1040987213401</v>
       </c>
       <c r="N64">
-        <v>-14.38927175750933</v>
+        <v>-15.99409872134012</v>
       </c>
       <c r="O64">
-        <v>-2.1583907636264</v>
+        <v>-2.399114808201019</v>
       </c>
       <c r="P64">
-        <v>-12.23088099388293</v>
+        <v>-13.5949839131391</v>
       </c>
       <c r="Q64">
-        <v>84.86911900611706</v>
+        <v>83.50501608686089</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1162568975163376</v>
+        <v>0.1181611379897521</v>
       </c>
       <c r="T64">
-        <v>1.290442821452102</v>
+        <v>1.325319654464321</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1283074717482693</v>
+        <v>0.1262708452125825</v>
       </c>
       <c r="W64">
-        <v>0.1279644631473541</v>
+        <v>0.1282634399227929</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8553831449884621</v>
+        <v>0.84180563475055</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1245255882075678</v>
+        <v>0.1255355882075678</v>
       </c>
       <c r="C65">
-        <v>-35.77906446148006</v>
+        <v>-52.00906398768063</v>
       </c>
       <c r="D65">
-        <v>646.1009540762592</v>
+        <v>640.8030183363719</v>
       </c>
       <c r="E65">
-        <v>545.5136399064071</v>
+        <v>556.4457036927204</v>
       </c>
       <c r="F65">
-        <v>688.7200185377393</v>
+        <v>699.6520823240526</v>
       </c>
       <c r="G65">
         <v>6.84</v>
@@ -6617,37 +6617,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M65">
-        <v>101.1040987213401</v>
+        <v>102.7089256851709</v>
       </c>
       <c r="N65">
-        <v>-15.99409872134012</v>
+        <v>-17.59892568517091</v>
       </c>
       <c r="O65">
-        <v>-2.399114808201019</v>
+        <v>-2.639838852775636</v>
       </c>
       <c r="P65">
-        <v>-13.5949839131391</v>
+        <v>-14.95908683239528</v>
       </c>
       <c r="Q65">
-        <v>83.50501608686089</v>
+        <v>82.14091316760472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1181611379897521</v>
+        <v>0.1201711696005786</v>
       </c>
       <c r="T65">
-        <v>1.325319654464321</v>
+        <v>1.362134089310552</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1262708452125825</v>
+        <v>0.1242978632561359</v>
       </c>
       <c r="W65">
-        <v>0.1282634399227929</v>
+        <v>0.1285530736739993</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.84180563475055</v>
+        <v>0.8286524217075728</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1255355882075678</v>
+        <v>0.1265455882075678</v>
       </c>
       <c r="C66">
-        <v>-52.00906398768063</v>
+        <v>-68.15288552511674</v>
       </c>
       <c r="D66">
-        <v>640.8030183363719</v>
+        <v>635.5912605852492</v>
       </c>
       <c r="E66">
-        <v>556.4457036927204</v>
+        <v>567.3777674790338</v>
       </c>
       <c r="F66">
-        <v>699.6520823240526</v>
+        <v>710.584146110366</v>
       </c>
       <c r="G66">
         <v>6.84</v>
@@ -6699,37 +6699,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M66">
-        <v>102.7089256851709</v>
+        <v>104.3137526490017</v>
       </c>
       <c r="N66">
-        <v>-17.59892568517091</v>
+        <v>-19.20375264900171</v>
       </c>
       <c r="O66">
-        <v>-2.639838852775636</v>
+        <v>-2.880562897350257</v>
       </c>
       <c r="P66">
-        <v>-14.95908683239528</v>
+        <v>-16.32318975165146</v>
       </c>
       <c r="Q66">
-        <v>82.14091316760472</v>
+        <v>80.77681024834854</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1201711696005786</v>
+        <v>0.1222960601605951</v>
       </c>
       <c r="T66">
-        <v>1.362134089310552</v>
+        <v>1.401052206147997</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1242978632561359</v>
+        <v>0.1223855884368107</v>
       </c>
       <c r="W66">
-        <v>0.1285530736739993</v>
+        <v>0.1288337956174762</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8286524217075728</v>
+        <v>0.8159039229120716</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1265455882075678</v>
+        <v>0.1275555882075678</v>
       </c>
       <c r="C67">
-        <v>-68.15288552511674</v>
+        <v>-84.21261480998533</v>
       </c>
       <c r="D67">
-        <v>635.5912605852492</v>
+        <v>630.4635950866939</v>
       </c>
       <c r="E67">
-        <v>567.3777674790338</v>
+        <v>578.309831265347</v>
       </c>
       <c r="F67">
-        <v>710.584146110366</v>
+        <v>721.5162098966792</v>
       </c>
       <c r="G67">
         <v>6.84</v>
@@ -6781,37 +6781,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M67">
-        <v>104.3137526490017</v>
+        <v>105.9185796128325</v>
       </c>
       <c r="N67">
-        <v>-19.20375264900171</v>
+        <v>-20.8085796128325</v>
       </c>
       <c r="O67">
-        <v>-2.880562897350257</v>
+        <v>-3.121286941924875</v>
       </c>
       <c r="P67">
-        <v>-16.32318975165146</v>
+        <v>-17.68729267090763</v>
       </c>
       <c r="Q67">
-        <v>80.77681024834854</v>
+        <v>79.41270732909237</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1222960601605951</v>
+        <v>0.1245459442829656</v>
       </c>
       <c r="T67">
-        <v>1.401052206147997</v>
+        <v>1.442259623975879</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1223855884368107</v>
+        <v>0.1205312613392833</v>
       </c>
       <c r="W67">
-        <v>0.1288337956174762</v>
+        <v>0.1291060108353932</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8159039229120716</v>
+        <v>0.8035417422618888</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1275555882075678</v>
+        <v>0.1653678611205404</v>
       </c>
       <c r="C68">
-        <v>-84.21261480998533</v>
+        <v>-241.3932000941261</v>
       </c>
       <c r="D68">
-        <v>630.4635950866939</v>
+        <v>484.2150735888666</v>
       </c>
       <c r="E68">
-        <v>578.309831265347</v>
+        <v>589.2418950516604</v>
       </c>
       <c r="F68">
-        <v>721.5162098966792</v>
+        <v>732.4482736829926</v>
       </c>
       <c r="G68">
         <v>6.84</v>
@@ -6863,45 +6863,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M68">
-        <v>105.9185796128325</v>
+        <v>147.0756133555449</v>
       </c>
       <c r="N68">
-        <v>-20.8085796128325</v>
+        <v>-61.96561335554492</v>
       </c>
       <c r="O68">
-        <v>-3.121286941924875</v>
+        <v>-9.294842003331738</v>
       </c>
       <c r="P68">
-        <v>-17.68729267090763</v>
+        <v>-52.67077135221318</v>
       </c>
       <c r="Q68">
-        <v>79.41270732909237</v>
+        <v>44.42922864778681</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1245459442829656</v>
+        <v>0.1288178605126695</v>
       </c>
       <c r="T68">
-        <v>1.442259623975879</v>
+        <v>1.520501269957919</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1205312613392833</v>
+        <v>0.08680228971160493</v>
       </c>
       <c r="W68">
-        <v>0.1291060108353932</v>
+        <v>0.1833701002259097</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8035417422618888</v>
+        <v>0.5786819314106995</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1653678611205404</v>
+        <v>0.1669178611205404</v>
       </c>
       <c r="C69">
-        <v>-241.3932000941261</v>
+        <v>-256.8862477499765</v>
       </c>
       <c r="D69">
-        <v>484.2150735888666</v>
+        <v>479.6540897193294</v>
       </c>
       <c r="E69">
-        <v>589.2418950516604</v>
+        <v>600.1739588379737</v>
       </c>
       <c r="F69">
-        <v>732.4482736829926</v>
+        <v>743.3803374693059</v>
       </c>
       <c r="G69">
         <v>6.84</v>
@@ -6945,37 +6945,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M69">
-        <v>147.0756133555449</v>
+        <v>149.2707717638366</v>
       </c>
       <c r="N69">
-        <v>-61.96561335554492</v>
+        <v>-64.16077176383661</v>
       </c>
       <c r="O69">
-        <v>-9.294842003331738</v>
+        <v>-9.624115764575491</v>
       </c>
       <c r="P69">
-        <v>-52.67077135221318</v>
+        <v>-54.53665599926111</v>
       </c>
       <c r="Q69">
-        <v>44.42922864778681</v>
+        <v>42.56334400073888</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1288178605126695</v>
+        <v>0.1314121686536904</v>
       </c>
       <c r="T69">
-        <v>1.520501269957919</v>
+        <v>1.568016934644103</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08680228971160493</v>
+        <v>0.08552578545114016</v>
       </c>
       <c r="W69">
-        <v>0.1833701002259097</v>
+        <v>0.183626422281411</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5786819314106995</v>
+        <v>0.5701719030076011</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1669178611205404</v>
+        <v>0.1684678611205405</v>
       </c>
       <c r="C70">
-        <v>-256.8862477499765</v>
+        <v>-272.2941743220886</v>
       </c>
       <c r="D70">
-        <v>479.6540897193294</v>
+        <v>475.1782269335307</v>
       </c>
       <c r="E70">
-        <v>600.1739588379737</v>
+        <v>611.1060226242871</v>
       </c>
       <c r="F70">
-        <v>743.3803374693059</v>
+        <v>754.3124012556193</v>
       </c>
       <c r="G70">
         <v>6.84</v>
@@ -7027,37 +7027,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M70">
-        <v>149.2707717638366</v>
+        <v>151.4659301721284</v>
       </c>
       <c r="N70">
-        <v>-64.16077176383661</v>
+        <v>-66.35593017212835</v>
       </c>
       <c r="O70">
-        <v>-9.624115764575491</v>
+        <v>-9.953389525819253</v>
       </c>
       <c r="P70">
-        <v>-54.53665599926111</v>
+        <v>-56.4025406463091</v>
       </c>
       <c r="Q70">
-        <v>42.56334400073888</v>
+        <v>40.6974593536909</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1314121686536904</v>
+        <v>0.1341738515134869</v>
       </c>
       <c r="T70">
-        <v>1.568016934644103</v>
+        <v>1.618598126084236</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08552578545114016</v>
+        <v>0.08428628131416709</v>
       </c>
       <c r="W70">
-        <v>0.183626422281411</v>
+        <v>0.1838753147121153</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5701719030076011</v>
+        <v>0.5619085420944474</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1684678611205405</v>
+        <v>0.1700178611205405</v>
       </c>
       <c r="C71">
-        <v>-272.2941743220886</v>
+        <v>-287.6193406866421</v>
       </c>
       <c r="D71">
-        <v>475.1782269335307</v>
+        <v>470.7851243552905</v>
       </c>
       <c r="E71">
-        <v>611.1060226242871</v>
+        <v>622.0380864106004</v>
       </c>
       <c r="F71">
-        <v>754.3124012556193</v>
+        <v>765.2444650419326</v>
       </c>
       <c r="G71">
         <v>6.84</v>
@@ -7109,37 +7109,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M71">
-        <v>151.4659301721284</v>
+        <v>153.6610885804201</v>
       </c>
       <c r="N71">
-        <v>-66.35593017212835</v>
+        <v>-68.55108858042004</v>
       </c>
       <c r="O71">
-        <v>-9.953389525819253</v>
+        <v>-10.28266328706301</v>
       </c>
       <c r="P71">
-        <v>-56.4025406463091</v>
+        <v>-58.26842529335704</v>
       </c>
       <c r="Q71">
-        <v>40.6974593536909</v>
+        <v>38.83157470664295</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1341738515134869</v>
+        <v>0.1371196465639364</v>
       </c>
       <c r="T71">
-        <v>1.618598126084236</v>
+        <v>1.67255139695371</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08428628131416709</v>
+        <v>0.08308219158110758</v>
       </c>
       <c r="W71">
-        <v>0.1838753147121153</v>
+        <v>0.1841170959305136</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5619085420944474</v>
+        <v>0.5538812772073839</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1700178611205405</v>
+        <v>0.1715678611205405</v>
       </c>
       <c r="C72">
-        <v>-287.6193406866421</v>
+        <v>-302.8640212128007</v>
       </c>
       <c r="D72">
-        <v>470.7851243552905</v>
+        <v>466.4725076154454</v>
       </c>
       <c r="E72">
-        <v>622.0380864106004</v>
+        <v>632.9701501969138</v>
       </c>
       <c r="F72">
-        <v>765.2444650419326</v>
+        <v>776.176528828246</v>
       </c>
       <c r="G72">
         <v>6.84</v>
@@ -7191,37 +7191,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M72">
-        <v>153.6610885804201</v>
+        <v>155.8562469887118</v>
       </c>
       <c r="N72">
-        <v>-68.55108858042004</v>
+        <v>-70.74624698871179</v>
       </c>
       <c r="O72">
-        <v>-10.28266328706301</v>
+        <v>-10.61193704830677</v>
       </c>
       <c r="P72">
-        <v>-58.26842529335704</v>
+        <v>-60.13430994040502</v>
       </c>
       <c r="Q72">
-        <v>38.83157470664295</v>
+        <v>36.96569005959498</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1371196465639364</v>
+        <v>0.1402685998937274</v>
       </c>
       <c r="T72">
-        <v>1.67255139695371</v>
+        <v>1.730225583055563</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08308219158110758</v>
+        <v>0.0819120198686976</v>
       </c>
       <c r="W72">
-        <v>0.1841170959305136</v>
+        <v>0.1843520664103655</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5538812772073839</v>
+        <v>0.546080132457984</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1715678611205405</v>
+        <v>0.1731178611205405</v>
       </c>
       <c r="C73">
-        <v>-302.8640212128005</v>
+        <v>-318.0304076889731</v>
       </c>
       <c r="D73">
-        <v>466.4725076154454</v>
+        <v>462.2381849255861</v>
       </c>
       <c r="E73">
-        <v>632.9701501969137</v>
+        <v>643.9022139832269</v>
       </c>
       <c r="F73">
-        <v>776.1765288282459</v>
+        <v>787.1085926145591</v>
       </c>
       <c r="G73">
         <v>6.84</v>
@@ -7273,37 +7273,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M73">
-        <v>155.8562469887118</v>
+        <v>158.0514053970035</v>
       </c>
       <c r="N73">
-        <v>-70.74624698871176</v>
+        <v>-72.94140539700348</v>
       </c>
       <c r="O73">
-        <v>-10.61193704830676</v>
+        <v>-10.94121080955052</v>
       </c>
       <c r="P73">
-        <v>-60.134309940405</v>
+        <v>-62.00019458745296</v>
       </c>
       <c r="Q73">
-        <v>36.965690059595</v>
+        <v>35.09980541254703</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1402685998937273</v>
+        <v>0.1436424784613604</v>
       </c>
       <c r="T73">
-        <v>1.730225583055562</v>
+        <v>1.792019353878975</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08191201986869762</v>
+        <v>0.08077435292607682</v>
       </c>
       <c r="W73">
-        <v>0.1843520664103655</v>
+        <v>0.1845805099324438</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.546080132457984</v>
+        <v>0.5384956861738455</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1731178611205405</v>
+        <v>0.1746678611205404</v>
       </c>
       <c r="C74">
-        <v>-318.0304076889731</v>
+        <v>-333.1206130371589</v>
       </c>
       <c r="D74">
-        <v>462.2381849255861</v>
+        <v>458.0800433637136</v>
       </c>
       <c r="E74">
-        <v>643.9022139832269</v>
+        <v>654.8342777695403</v>
       </c>
       <c r="F74">
-        <v>787.1085926145591</v>
+        <v>798.0406564008725</v>
       </c>
       <c r="G74">
         <v>6.84</v>
@@ -7355,37 +7355,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M74">
-        <v>158.0514053970035</v>
+        <v>160.2465638052952</v>
       </c>
       <c r="N74">
-        <v>-72.94140539700348</v>
+        <v>-75.1365638052952</v>
       </c>
       <c r="O74">
-        <v>-10.94121080955052</v>
+        <v>-11.27048457079428</v>
       </c>
       <c r="P74">
-        <v>-62.00019458745296</v>
+        <v>-63.86607923450092</v>
       </c>
       <c r="Q74">
-        <v>35.09980541254703</v>
+        <v>33.23392076549908</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1436424784613604</v>
+        <v>0.1472662739599293</v>
       </c>
       <c r="T74">
-        <v>1.792019353878975</v>
+        <v>1.858390441059678</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08077435292607682</v>
+        <v>0.0796678549407881</v>
       </c>
       <c r="W74">
-        <v>0.1845805099324438</v>
+        <v>0.1848026947278898</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5384956861738455</v>
+        <v>0.5311190329385873</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1746678611205404</v>
+        <v>0.1762178611205404</v>
       </c>
       <c r="C75">
-        <v>-333.1206130371589</v>
+        <v>-348.1366748286027</v>
       </c>
       <c r="D75">
-        <v>458.0800433637136</v>
+        <v>453.9960453585831</v>
       </c>
       <c r="E75">
-        <v>654.8342777695403</v>
+        <v>665.7663415558536</v>
       </c>
       <c r="F75">
-        <v>798.0406564008725</v>
+        <v>808.9727201871858</v>
       </c>
       <c r="G75">
         <v>6.84</v>
@@ -7437,37 +7437,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M75">
-        <v>160.2465638052952</v>
+        <v>162.4417222135869</v>
       </c>
       <c r="N75">
-        <v>-75.1365638052952</v>
+        <v>-77.33172221358691</v>
       </c>
       <c r="O75">
-        <v>-11.27048457079428</v>
+        <v>-11.59975833203804</v>
       </c>
       <c r="P75">
-        <v>-63.86607923450092</v>
+        <v>-65.73196388154888</v>
       </c>
       <c r="Q75">
-        <v>33.23392076549908</v>
+        <v>31.36803611845112</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1472662739599293</v>
+        <v>0.1511688229583882</v>
       </c>
       <c r="T75">
-        <v>1.858390441059678</v>
+        <v>1.92986699648505</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0796678549407881</v>
+        <v>0.07859126230645312</v>
       </c>
       <c r="W75">
-        <v>0.1848026947278898</v>
+        <v>0.1850188745288642</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5311190329385873</v>
+        <v>0.5239417487096875</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1762178611205404</v>
+        <v>0.1777678611205404</v>
       </c>
       <c r="C76">
-        <v>-348.1366748286027</v>
+        <v>-363.0805586130494</v>
       </c>
       <c r="D76">
-        <v>453.9960453585831</v>
+        <v>449.9842253604498</v>
       </c>
       <c r="E76">
-        <v>665.7663415558536</v>
+        <v>676.698405342167</v>
       </c>
       <c r="F76">
-        <v>808.9727201871858</v>
+        <v>819.9047839734992</v>
       </c>
       <c r="G76">
         <v>6.84</v>
@@ -7519,37 +7519,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M76">
-        <v>162.4417222135869</v>
+        <v>164.6368806218786</v>
       </c>
       <c r="N76">
-        <v>-77.33172221358691</v>
+        <v>-79.52688062187863</v>
       </c>
       <c r="O76">
-        <v>-11.59975833203804</v>
+        <v>-11.92903209328179</v>
       </c>
       <c r="P76">
-        <v>-65.73196388154888</v>
+        <v>-67.59784852859684</v>
       </c>
       <c r="Q76">
-        <v>31.36803611845112</v>
+        <v>29.50215147140315</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1511688229583882</v>
+        <v>0.1553835758767237</v>
       </c>
       <c r="T76">
-        <v>1.92986699648505</v>
+        <v>2.007061676344452</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07859126230645312</v>
+        <v>0.07754337880903374</v>
       </c>
       <c r="W76">
-        <v>0.1850188745288642</v>
+        <v>0.185229289535146</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5239417487096875</v>
+        <v>0.5169558587268916</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1777678611205404</v>
+        <v>0.1793178611205404</v>
       </c>
       <c r="C77">
-        <v>-363.0805586130494</v>
+        <v>-377.9541610730261</v>
       </c>
       <c r="D77">
-        <v>449.9842253604498</v>
+        <v>446.0426866867864</v>
       </c>
       <c r="E77">
-        <v>676.698405342167</v>
+        <v>687.6304691284803</v>
       </c>
       <c r="F77">
-        <v>819.9047839734992</v>
+        <v>830.8368477598125</v>
       </c>
       <c r="G77">
         <v>6.84</v>
@@ -7601,37 +7601,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M77">
-        <v>164.6368806218786</v>
+        <v>166.8320390301704</v>
       </c>
       <c r="N77">
-        <v>-79.52688062187863</v>
+        <v>-81.72203903017035</v>
       </c>
       <c r="O77">
-        <v>-11.92903209328179</v>
+        <v>-12.25830585452555</v>
       </c>
       <c r="P77">
-        <v>-67.59784852859684</v>
+        <v>-69.46373317564479</v>
       </c>
       <c r="Q77">
-        <v>29.50215147140315</v>
+        <v>27.6362668243552</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1553835758767237</v>
+        <v>0.1599495582049205</v>
       </c>
       <c r="T77">
-        <v>2.007061676344452</v>
+        <v>2.090689246192138</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07754337880903374</v>
+        <v>0.07652307119312539</v>
       </c>
       <c r="W77">
-        <v>0.185229289535146</v>
+        <v>0.1854341673044204</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5169558587268916</v>
+        <v>0.5101538079541693</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1793178611205404</v>
+        <v>0.1808678611205405</v>
       </c>
       <c r="C78">
-        <v>-377.9541610730261</v>
+        <v>-392.7593130137906</v>
       </c>
       <c r="D78">
-        <v>446.0426866867864</v>
+        <v>442.1695985323352</v>
       </c>
       <c r="E78">
-        <v>687.6304691284803</v>
+        <v>698.5625329147936</v>
       </c>
       <c r="F78">
-        <v>830.8368477598125</v>
+        <v>841.7689115461258</v>
       </c>
       <c r="G78">
         <v>6.84</v>
@@ -7683,37 +7683,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M78">
-        <v>166.8320390301704</v>
+        <v>169.0271974384621</v>
       </c>
       <c r="N78">
-        <v>-81.72203903017035</v>
+        <v>-83.91719743846204</v>
       </c>
       <c r="O78">
-        <v>-12.25830585452555</v>
+        <v>-12.58757961576931</v>
       </c>
       <c r="P78">
-        <v>-69.46373317564479</v>
+        <v>-71.32961782269274</v>
       </c>
       <c r="Q78">
-        <v>27.6362668243552</v>
+        <v>25.77038217730725</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1599495582049205</v>
+        <v>0.1649125824746997</v>
       </c>
       <c r="T78">
-        <v>2.090689246192138</v>
+        <v>2.181588778635274</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07652307119312539</v>
+        <v>0.07552926507373416</v>
       </c>
       <c r="W78">
-        <v>0.1854341673044204</v>
+        <v>0.1856337235731942</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5101538079541693</v>
+        <v>0.5035284338248944</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1808678611205405</v>
+        <v>0.2099689557571482</v>
       </c>
       <c r="C79">
-        <v>-392.7593130137906</v>
+        <v>-465.6722658462892</v>
       </c>
       <c r="D79">
-        <v>442.1695985323352</v>
+        <v>380.1887094861499</v>
       </c>
       <c r="E79">
-        <v>698.5625329147936</v>
+        <v>709.494596701107</v>
       </c>
       <c r="F79">
-        <v>841.7689115461258</v>
+        <v>852.7009753324392</v>
       </c>
       <c r="G79">
         <v>6.84</v>
@@ -7765,45 +7765,45 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M79">
-        <v>169.0271974384621</v>
+        <v>201.0668899833892</v>
       </c>
       <c r="N79">
-        <v>-83.91719743846204</v>
+        <v>-115.9568899833891</v>
       </c>
       <c r="O79">
-        <v>-12.58757961576931</v>
+        <v>-17.39353349750837</v>
       </c>
       <c r="P79">
-        <v>-71.32961782269274</v>
+        <v>-98.56335648588077</v>
       </c>
       <c r="Q79">
-        <v>25.77038217730725</v>
+        <v>-1.46335648588078</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1649125824746997</v>
+        <v>0.171468130026312</v>
       </c>
       <c r="T79">
-        <v>2.181588778635274</v>
+        <v>2.301655934256261</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07552926507373416</v>
+        <v>0.06349379552772058</v>
       </c>
       <c r="W79">
-        <v>0.1856337235731942</v>
+        <v>0.2208281630145635</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5035284338248944</v>
+        <v>0.4232919701848039</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2099689557571482</v>
+        <v>0.2118689557571482</v>
       </c>
       <c r="C80">
-        <v>-465.6722658462892</v>
+        <v>-480.0522390968409</v>
       </c>
       <c r="D80">
-        <v>380.1887094861499</v>
+        <v>376.7408000219115</v>
       </c>
       <c r="E80">
-        <v>709.494596701107</v>
+        <v>720.4266604874202</v>
       </c>
       <c r="F80">
-        <v>852.7009753324392</v>
+        <v>863.6330391187524</v>
       </c>
       <c r="G80">
         <v>6.84</v>
@@ -7847,37 +7847,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M80">
-        <v>201.0668899833892</v>
+        <v>203.6446706242018</v>
       </c>
       <c r="N80">
-        <v>-115.9568899833891</v>
+        <v>-118.5346706242018</v>
       </c>
       <c r="O80">
-        <v>-17.39353349750837</v>
+        <v>-17.78020059363027</v>
       </c>
       <c r="P80">
-        <v>-98.56335648588077</v>
+        <v>-100.7544700305716</v>
       </c>
       <c r="Q80">
-        <v>-1.46335648588078</v>
+        <v>-3.654470030571559</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.171468130026312</v>
+        <v>0.1774523266942317</v>
       </c>
       <c r="T80">
-        <v>2.301655934256261</v>
+        <v>2.411258597792274</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06349379552772058</v>
+        <v>0.06269007659698994</v>
       </c>
       <c r="W80">
-        <v>0.2208281630145635</v>
+        <v>0.2210176799384298</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4232919701848039</v>
+        <v>0.4179338439799329</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2118689557571482</v>
+        <v>0.2137689557571482</v>
       </c>
       <c r="C81">
-        <v>-480.0522390968409</v>
+        <v>-494.3702366178281</v>
       </c>
       <c r="D81">
-        <v>376.7408000219115</v>
+        <v>373.3548662872378</v>
       </c>
       <c r="E81">
-        <v>720.4266604874202</v>
+        <v>731.3587242737336</v>
       </c>
       <c r="F81">
-        <v>863.6330391187524</v>
+        <v>874.5651029050658</v>
       </c>
       <c r="G81">
         <v>6.84</v>
@@ -7929,37 +7929,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M81">
-        <v>203.6446706242018</v>
+        <v>206.2224512650145</v>
       </c>
       <c r="N81">
-        <v>-118.5346706242018</v>
+        <v>-121.1124512650145</v>
       </c>
       <c r="O81">
-        <v>-17.78020059363027</v>
+        <v>-18.16686768975218</v>
       </c>
       <c r="P81">
-        <v>-100.7544700305716</v>
+        <v>-102.9455835752623</v>
       </c>
       <c r="Q81">
-        <v>-3.654470030571559</v>
+        <v>-5.845583575262353</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1774523266942317</v>
+        <v>0.1840349430289432</v>
       </c>
       <c r="T81">
-        <v>2.411258597792274</v>
+        <v>2.531821527681887</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06269007659698994</v>
+        <v>0.06190645063952756</v>
       </c>
       <c r="W81">
-        <v>0.2210176799384298</v>
+        <v>0.2212024589391994</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4179338439799329</v>
+        <v>0.4127096709301837</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2137689557571482</v>
+        <v>0.2156689557571482</v>
       </c>
       <c r="C82">
-        <v>-494.3702366178281</v>
+        <v>-508.6279145336019</v>
       </c>
       <c r="D82">
-        <v>373.3548662872378</v>
+        <v>370.0292521577772</v>
       </c>
       <c r="E82">
-        <v>731.3587242737336</v>
+        <v>742.2907880600469</v>
       </c>
       <c r="F82">
-        <v>874.5651029050658</v>
+        <v>885.4971666913791</v>
       </c>
       <c r="G82">
         <v>6.84</v>
@@ -8011,37 +8011,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M82">
-        <v>206.2224512650145</v>
+        <v>208.8002319058272</v>
       </c>
       <c r="N82">
-        <v>-121.1124512650145</v>
+        <v>-123.6902319058272</v>
       </c>
       <c r="O82">
-        <v>-18.16686768975218</v>
+        <v>-18.55353478587407</v>
       </c>
       <c r="P82">
-        <v>-102.9455835752623</v>
+        <v>-105.1366971199531</v>
       </c>
       <c r="Q82">
-        <v>-5.845583575262353</v>
+        <v>-8.036697119953104</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1840349430289432</v>
+        <v>0.1913104663462561</v>
       </c>
       <c r="T82">
-        <v>2.531821527681887</v>
+        <v>2.665075292296724</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06190645063952756</v>
+        <v>0.06114217347113834</v>
       </c>
       <c r="W82">
-        <v>0.2212024589391994</v>
+        <v>0.2213826754955056</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4127096709301837</v>
+        <v>0.407614489807589</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2156689557571482</v>
+        <v>0.2175689557571482</v>
       </c>
       <c r="C83">
-        <v>-508.6279145336019</v>
+        <v>-522.8268704825471</v>
       </c>
       <c r="D83">
-        <v>370.0292521577772</v>
+        <v>366.7623599951455</v>
       </c>
       <c r="E83">
-        <v>742.2907880600469</v>
+        <v>753.2228518463603</v>
       </c>
       <c r="F83">
-        <v>885.4971666913791</v>
+        <v>896.4292304776925</v>
       </c>
       <c r="G83">
         <v>6.84</v>
@@ -8093,37 +8093,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M83">
-        <v>208.8002319058272</v>
+        <v>211.3780125466399</v>
       </c>
       <c r="N83">
-        <v>-123.6902319058272</v>
+        <v>-126.2680125466399</v>
       </c>
       <c r="O83">
-        <v>-18.55353478587407</v>
+        <v>-18.94020188199598</v>
       </c>
       <c r="P83">
-        <v>-105.1366971199531</v>
+        <v>-107.3278106646439</v>
       </c>
       <c r="Q83">
-        <v>-8.036697119953104</v>
+        <v>-10.2278106646439</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1913104663462561</v>
+        <v>0.1993943811432703</v>
       </c>
       <c r="T83">
-        <v>2.665075292296724</v>
+        <v>2.813135030757653</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06114217347113834</v>
+        <v>0.06039653720929519</v>
       </c>
       <c r="W83">
-        <v>0.2213826754955056</v>
+        <v>0.2215584965260482</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.407614489807589</v>
+        <v>0.4026435813953013</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2175689557571482</v>
+        <v>0.2194689557571482</v>
       </c>
       <c r="C84">
-        <v>-522.8268704825471</v>
+        <v>-536.9686461762727</v>
       </c>
       <c r="D84">
-        <v>366.7623599951455</v>
+        <v>363.5526480877331</v>
       </c>
       <c r="E84">
-        <v>753.2228518463603</v>
+        <v>764.1549156326736</v>
       </c>
       <c r="F84">
-        <v>896.4292304776925</v>
+        <v>907.3612942640058</v>
       </c>
       <c r="G84">
         <v>6.84</v>
@@ -8175,37 +8175,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M84">
-        <v>211.3780125466399</v>
+        <v>213.9557931874526</v>
       </c>
       <c r="N84">
-        <v>-126.2680125466399</v>
+        <v>-128.8457931874526</v>
       </c>
       <c r="O84">
-        <v>-18.94020188199598</v>
+        <v>-19.32686897811788</v>
       </c>
       <c r="P84">
-        <v>-107.3278106646439</v>
+        <v>-109.5189242093347</v>
       </c>
       <c r="Q84">
-        <v>-10.2278106646439</v>
+        <v>-12.41892420933468</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1993943811432703</v>
+        <v>0.2084293447399333</v>
       </c>
       <c r="T84">
-        <v>2.813135030757653</v>
+        <v>2.978613561978692</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06039653720929519</v>
+        <v>0.05966886808629163</v>
       </c>
       <c r="W84">
-        <v>0.2215584965260482</v>
+        <v>0.2217300809052524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4026435813953013</v>
+        <v>0.397792453908611</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2194689557571482</v>
+        <v>0.2213689557571482</v>
       </c>
       <c r="C85">
-        <v>-536.9686461762727</v>
+        <v>-551.0547298255933</v>
       </c>
       <c r="D85">
-        <v>363.5526480877331</v>
+        <v>360.3986282247259</v>
       </c>
       <c r="E85">
-        <v>764.1549156326736</v>
+        <v>775.086979418987</v>
       </c>
       <c r="F85">
-        <v>907.3612942640058</v>
+        <v>918.2933580503192</v>
       </c>
       <c r="G85">
         <v>6.84</v>
@@ -8257,37 +8257,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M85">
-        <v>213.9557931874526</v>
+        <v>216.5335738282653</v>
       </c>
       <c r="N85">
-        <v>-128.8457931874526</v>
+        <v>-131.4235738282653</v>
       </c>
       <c r="O85">
-        <v>-19.32686897811788</v>
+        <v>-19.71353607423979</v>
       </c>
       <c r="P85">
-        <v>-109.5189242093347</v>
+        <v>-111.7100377540255</v>
       </c>
       <c r="Q85">
-        <v>-12.41892420933468</v>
+        <v>-14.61003775402548</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2084293447399333</v>
+        <v>0.2185936787861791</v>
       </c>
       <c r="T85">
-        <v>2.978613561978692</v>
+        <v>3.164776909602361</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05966886808629163</v>
+        <v>0.05895852441859768</v>
       </c>
       <c r="W85">
-        <v>0.2217300809052524</v>
+        <v>0.2218975799420947</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.397792453908611</v>
+        <v>0.3930568294573179</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2213689557571482</v>
+        <v>0.2232689557571482</v>
       </c>
       <c r="C86">
-        <v>-551.0547298255932</v>
+        <v>-565.0865584413095</v>
       </c>
       <c r="D86">
-        <v>360.3986282247259</v>
+        <v>357.2988633953228</v>
       </c>
       <c r="E86">
-        <v>775.0869794189869</v>
+        <v>786.0190432053001</v>
       </c>
       <c r="F86">
-        <v>918.2933580503191</v>
+        <v>929.2254218366323</v>
       </c>
       <c r="G86">
         <v>6.84</v>
@@ -8339,37 +8339,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M86">
-        <v>216.5335738282652</v>
+        <v>219.1113544690779</v>
       </c>
       <c r="N86">
-        <v>-131.4235738282652</v>
+        <v>-134.0013544690779</v>
       </c>
       <c r="O86">
-        <v>-19.71353607423978</v>
+        <v>-20.10020317036168</v>
       </c>
       <c r="P86">
-        <v>-111.7100377540254</v>
+        <v>-113.9011512987162</v>
       </c>
       <c r="Q86">
-        <v>-14.61003775402546</v>
+        <v>-16.80115129871623</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.218593678786179</v>
+        <v>0.2301132573719243</v>
       </c>
       <c r="T86">
-        <v>3.164776909602359</v>
+        <v>3.375762036909183</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05895852441859768</v>
+        <v>0.05826489471955536</v>
       </c>
       <c r="W86">
-        <v>0.2218975799420947</v>
+        <v>0.2220611378251289</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3930568294573179</v>
+        <v>0.3884326314637024</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2232689557571482</v>
+        <v>0.2251689557571482</v>
       </c>
       <c r="C87">
-        <v>-565.0865584413095</v>
+        <v>-579.0655200172746</v>
       </c>
       <c r="D87">
-        <v>357.2988633953228</v>
+        <v>354.2519656056712</v>
       </c>
       <c r="E87">
-        <v>786.0190432053001</v>
+        <v>796.9511069916135</v>
       </c>
       <c r="F87">
-        <v>929.2254218366323</v>
+        <v>940.1574856229457</v>
       </c>
       <c r="G87">
         <v>6.84</v>
@@ -8421,37 +8421,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M87">
-        <v>219.1113544690779</v>
+        <v>221.6891351098906</v>
       </c>
       <c r="N87">
-        <v>-134.0013544690779</v>
+        <v>-136.5791351098906</v>
       </c>
       <c r="O87">
-        <v>-20.10020317036168</v>
+        <v>-20.48687026648359</v>
       </c>
       <c r="P87">
-        <v>-113.9011512987162</v>
+        <v>-116.092264843407</v>
       </c>
       <c r="Q87">
-        <v>-16.80115129871623</v>
+        <v>-18.992264843407</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2301132573719243</v>
+        <v>0.2432784900413474</v>
       </c>
       <c r="T87">
-        <v>3.375762036909183</v>
+        <v>3.61688789668841</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05826489471955536</v>
+        <v>0.05758739594374658</v>
       </c>
       <c r="W87">
-        <v>0.2220611378251289</v>
+        <v>0.2222208920364646</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3884326314637024</v>
+        <v>0.3839159729583106</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2251689557571482</v>
+        <v>0.2270689557571482</v>
       </c>
       <c r="C88">
-        <v>-579.0655200172746</v>
+        <v>-592.9929556027016</v>
       </c>
       <c r="D88">
-        <v>354.2519656056712</v>
+        <v>351.2565938065575</v>
       </c>
       <c r="E88">
-        <v>796.9511069916135</v>
+        <v>807.8831707779268</v>
       </c>
       <c r="F88">
-        <v>940.1574856229457</v>
+        <v>951.089549409259</v>
       </c>
       <c r="G88">
         <v>6.84</v>
@@ -8503,37 +8503,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M88">
-        <v>221.6891351098906</v>
+        <v>224.2669157507033</v>
       </c>
       <c r="N88">
-        <v>-136.5791351098906</v>
+        <v>-139.1569157507033</v>
       </c>
       <c r="O88">
-        <v>-20.48687026648359</v>
+        <v>-20.87353736260549</v>
       </c>
       <c r="P88">
-        <v>-116.092264843407</v>
+        <v>-118.2833783880978</v>
       </c>
       <c r="Q88">
-        <v>-18.992264843407</v>
+        <v>-21.18337838809778</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2432784900413474</v>
+        <v>0.2584691431214511</v>
       </c>
       <c r="T88">
-        <v>3.61688789668841</v>
+        <v>3.895110042587519</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05758739594374658</v>
+        <v>0.05692547185243915</v>
       </c>
       <c r="W88">
-        <v>0.2222208920364646</v>
+        <v>0.2223769737371949</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3839159729583106</v>
+        <v>0.3795031456829276</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2270689557571482</v>
+        <v>0.2289689557571482</v>
       </c>
       <c r="C89">
-        <v>-592.9929556027016</v>
+        <v>-606.870161270223</v>
       </c>
       <c r="D89">
-        <v>351.2565938065575</v>
+        <v>348.3114519253493</v>
       </c>
       <c r="E89">
-        <v>807.8831707779268</v>
+        <v>818.8152345642401</v>
       </c>
       <c r="F89">
-        <v>951.089549409259</v>
+        <v>962.0216131955723</v>
       </c>
       <c r="G89">
         <v>6.84</v>
@@ -8585,37 +8585,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M89">
-        <v>224.2669157507033</v>
+        <v>226.844696391516</v>
       </c>
       <c r="N89">
-        <v>-139.1569157507033</v>
+        <v>-141.7346963915159</v>
       </c>
       <c r="O89">
-        <v>-20.87353736260549</v>
+        <v>-21.26020445872739</v>
       </c>
       <c r="P89">
-        <v>-118.2833783880978</v>
+        <v>-120.4744919327886</v>
       </c>
       <c r="Q89">
-        <v>-21.18337838809778</v>
+        <v>-23.37449193278856</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2584691431214511</v>
+        <v>0.2761915717149054</v>
       </c>
       <c r="T89">
-        <v>3.895110042587519</v>
+        <v>4.219702546136479</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05692547185243915</v>
+        <v>0.05627859149047962</v>
       </c>
       <c r="W89">
-        <v>0.2223769737371949</v>
+        <v>0.2225295081265449</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3795031456829276</v>
+        <v>0.3751906099365308</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2289689557571482</v>
+        <v>0.2308689557571482</v>
       </c>
       <c r="C90">
-        <v>-606.870161270223</v>
+        <v>-620.698389985762</v>
       </c>
       <c r="D90">
-        <v>348.3114519253493</v>
+        <v>345.4152869961237</v>
       </c>
       <c r="E90">
-        <v>818.8152345642401</v>
+        <v>829.7472983505535</v>
       </c>
       <c r="F90">
-        <v>962.0216131955723</v>
+        <v>972.9536769818857</v>
       </c>
       <c r="G90">
         <v>6.84</v>
@@ -8667,37 +8667,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M90">
-        <v>226.844696391516</v>
+        <v>229.4224770323287</v>
       </c>
       <c r="N90">
-        <v>-141.7346963915159</v>
+        <v>-144.3124770323286</v>
       </c>
       <c r="O90">
-        <v>-21.26020445872739</v>
+        <v>-21.64687155484929</v>
       </c>
       <c r="P90">
-        <v>-120.4744919327886</v>
+        <v>-122.6656054774793</v>
       </c>
       <c r="Q90">
-        <v>-23.37449193278856</v>
+        <v>-25.56560547747935</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2761915717149054</v>
+        <v>0.2971362600526241</v>
       </c>
       <c r="T90">
-        <v>4.219702546136479</v>
+        <v>4.603311868512522</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05627859149047962</v>
+        <v>0.05564624776586748</v>
       </c>
       <c r="W90">
-        <v>0.2225295081265449</v>
+        <v>0.2226786147768084</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3751906099365308</v>
+        <v>0.3709749851057832</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2308689557571482</v>
+        <v>0.2327689557571482</v>
       </c>
       <c r="C91">
-        <v>-620.698389985762</v>
+        <v>-634.4788533858878</v>
       </c>
       <c r="D91">
-        <v>345.4152869961237</v>
+        <v>342.5668873823112</v>
       </c>
       <c r="E91">
-        <v>829.7472983505535</v>
+        <v>840.6793621368668</v>
       </c>
       <c r="F91">
-        <v>972.9536769818857</v>
+        <v>983.885740768199</v>
       </c>
       <c r="G91">
         <v>6.84</v>
@@ -8749,37 +8749,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M91">
-        <v>229.4224770323287</v>
+        <v>232.0002576731413</v>
       </c>
       <c r="N91">
-        <v>-144.3124770323286</v>
+        <v>-146.8902576731413</v>
       </c>
       <c r="O91">
-        <v>-21.64687155484929</v>
+        <v>-22.0335386509712</v>
       </c>
       <c r="P91">
-        <v>-122.6656054774793</v>
+        <v>-124.8567190221701</v>
       </c>
       <c r="Q91">
-        <v>-25.56560547747935</v>
+        <v>-27.75671902217013</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2971362600526241</v>
+        <v>0.3222698860578865</v>
       </c>
       <c r="T91">
-        <v>4.603311868512522</v>
+        <v>5.063643055363775</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05564624776586748</v>
+        <v>0.05502795612402451</v>
       </c>
       <c r="W91">
-        <v>0.2226786147768084</v>
+        <v>0.222824407945955</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3709749851057832</v>
+        <v>0.3668530408268301</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2327689557571482</v>
+        <v>0.2346689557571482</v>
       </c>
       <c r="C92">
-        <v>-634.4788533858878</v>
+        <v>-648.2127234679508</v>
       </c>
       <c r="D92">
-        <v>342.5668873823112</v>
+        <v>339.7650810865615</v>
       </c>
       <c r="E92">
-        <v>840.6793621368668</v>
+        <v>851.6114259231801</v>
       </c>
       <c r="F92">
-        <v>983.885740768199</v>
+        <v>994.8178045545123</v>
       </c>
       <c r="G92">
         <v>6.84</v>
@@ -8831,37 +8831,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M92">
-        <v>232.0002576731413</v>
+        <v>234.578038313954</v>
       </c>
       <c r="N92">
-        <v>-146.8902576731413</v>
+        <v>-149.468038313954</v>
       </c>
       <c r="O92">
-        <v>-22.0335386509712</v>
+        <v>-22.4202057470931</v>
       </c>
       <c r="P92">
-        <v>-124.8567190221701</v>
+        <v>-127.0478325668609</v>
       </c>
       <c r="Q92">
-        <v>-27.75671902217013</v>
+        <v>-29.94783256686091</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3222698860578865</v>
+        <v>0.3529887622865406</v>
       </c>
       <c r="T92">
-        <v>5.063643055363775</v>
+        <v>5.626270061515307</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05502795612402451</v>
+        <v>0.05442325330947479</v>
       </c>
       <c r="W92">
-        <v>0.222824407945955</v>
+        <v>0.2229669968696258</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3668530408268301</v>
+        <v>0.3628216887298319</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2346689557571482</v>
+        <v>0.2365689557571482</v>
       </c>
       <c r="C93">
-        <v>-648.2127234679508</v>
+        <v>-661.9011341979499</v>
       </c>
       <c r="D93">
-        <v>339.7650810865615</v>
+        <v>337.0087341428758</v>
       </c>
       <c r="E93">
-        <v>851.6114259231801</v>
+        <v>862.5434897094934</v>
       </c>
       <c r="F93">
-        <v>994.8178045545123</v>
+        <v>1005.749868340826</v>
       </c>
       <c r="G93">
         <v>6.84</v>
@@ -8913,37 +8913,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M93">
-        <v>234.578038313954</v>
+        <v>237.1558189547667</v>
       </c>
       <c r="N93">
-        <v>-149.468038313954</v>
+        <v>-152.0458189547667</v>
       </c>
       <c r="O93">
-        <v>-22.4202057470931</v>
+        <v>-22.806872843215</v>
       </c>
       <c r="P93">
-        <v>-127.0478325668609</v>
+        <v>-129.2389461115517</v>
       </c>
       <c r="Q93">
-        <v>-29.94783256686091</v>
+        <v>-32.13894611155169</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3529887622865406</v>
+        <v>0.3913873575723583</v>
       </c>
       <c r="T93">
-        <v>5.626270061515307</v>
+        <v>6.329553819204722</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05442325330947479</v>
+        <v>0.05383169620828485</v>
       </c>
       <c r="W93">
-        <v>0.2229669968696258</v>
+        <v>0.2231064860340864</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3628216887298319</v>
+        <v>0.358877974721899</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2365689557571482</v>
+        <v>0.2384689557571482</v>
       </c>
       <c r="C94">
-        <v>-661.9011341979499</v>
+        <v>-675.5451830407661</v>
       </c>
       <c r="D94">
-        <v>337.0087341428758</v>
+        <v>334.2967490863729</v>
       </c>
       <c r="E94">
-        <v>862.5434897094934</v>
+        <v>873.4755534958068</v>
       </c>
       <c r="F94">
-        <v>1005.749868340826</v>
+        <v>1016.681932127139</v>
       </c>
       <c r="G94">
         <v>6.84</v>
@@ -8995,37 +8995,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M94">
-        <v>237.1558189547667</v>
+        <v>239.7335995955794</v>
       </c>
       <c r="N94">
-        <v>-152.0458189547667</v>
+        <v>-154.6235995955794</v>
       </c>
       <c r="O94">
-        <v>-22.806872843215</v>
+        <v>-23.1935399393369</v>
       </c>
       <c r="P94">
-        <v>-129.2389461115517</v>
+        <v>-131.4300596562425</v>
       </c>
       <c r="Q94">
-        <v>-32.13894611155169</v>
+        <v>-34.33005965624247</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3913873575723583</v>
+        <v>0.4407569800826952</v>
       </c>
       <c r="T94">
-        <v>6.329553819204722</v>
+        <v>7.233775793376826</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05383169620828485</v>
+        <v>0.053252860765185</v>
       </c>
       <c r="W94">
-        <v>0.2231064860340864</v>
+        <v>0.2232429754315694</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.358877974721899</v>
+        <v>0.3550190717679</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2384689557571482</v>
+        <v>0.2403689557571482</v>
       </c>
       <c r="C95">
-        <v>-675.5451830407661</v>
+        <v>-689.1459324171028</v>
       </c>
       <c r="D95">
-        <v>334.2967490863729</v>
+        <v>331.6280634963495</v>
       </c>
       <c r="E95">
-        <v>873.4755534958068</v>
+        <v>884.4076172821201</v>
       </c>
       <c r="F95">
-        <v>1016.681932127139</v>
+        <v>1027.613995913452</v>
       </c>
       <c r="G95">
         <v>6.84</v>
@@ -9077,37 +9077,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M95">
-        <v>239.7335995955794</v>
+        <v>242.3113802363921</v>
       </c>
       <c r="N95">
-        <v>-154.6235995955794</v>
+        <v>-157.2013802363921</v>
       </c>
       <c r="O95">
-        <v>-23.1935399393369</v>
+        <v>-23.58020703545881</v>
       </c>
       <c r="P95">
-        <v>-131.4300596562425</v>
+        <v>-133.6211732009332</v>
       </c>
       <c r="Q95">
-        <v>-34.33005965624247</v>
+        <v>-36.52117320093325</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4407569800826952</v>
+        <v>0.5065831434298111</v>
       </c>
       <c r="T95">
-        <v>7.233775793376826</v>
+        <v>8.439405092272965</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.053252860765185</v>
+        <v>0.0526863409698107</v>
       </c>
       <c r="W95">
-        <v>0.2232429754315694</v>
+        <v>0.2233765607993186</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3550190717679</v>
+        <v>0.3512422731320713</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2403689557571482</v>
+        <v>0.2422689557571482</v>
       </c>
       <c r="C96">
-        <v>-689.1459324171028</v>
+        <v>-702.7044110911925</v>
       </c>
       <c r="D96">
-        <v>331.6280634963495</v>
+        <v>329.0016486085732</v>
       </c>
       <c r="E96">
-        <v>884.4076172821201</v>
+        <v>895.3396810684335</v>
       </c>
       <c r="F96">
-        <v>1027.613995913452</v>
+        <v>1038.546059699766</v>
       </c>
       <c r="G96">
         <v>6.84</v>
@@ -9159,37 +9159,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M96">
-        <v>242.3113802363921</v>
+        <v>244.8891608772048</v>
       </c>
       <c r="N96">
-        <v>-157.2013802363921</v>
+        <v>-159.7791608772048</v>
       </c>
       <c r="O96">
-        <v>-23.58020703545881</v>
+        <v>-23.96687413158071</v>
       </c>
       <c r="P96">
-        <v>-133.6211732009332</v>
+        <v>-135.812286745624</v>
       </c>
       <c r="Q96">
-        <v>-36.52117320093325</v>
+        <v>-38.71228674562406</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5065831434298111</v>
+        <v>0.5987397721157737</v>
       </c>
       <c r="T96">
-        <v>8.439405092272965</v>
+        <v>10.12728611072756</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0526863409698107</v>
+        <v>0.05213174790697058</v>
       </c>
       <c r="W96">
-        <v>0.2233765607993186</v>
+        <v>0.2235073338435363</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3512422731320713</v>
+        <v>0.3475449860464705</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2422689557571482</v>
+        <v>0.2441689557571482</v>
       </c>
       <c r="C97">
-        <v>-702.7044110911925</v>
+        <v>-716.2216154930804</v>
       </c>
       <c r="D97">
-        <v>329.0016486085732</v>
+        <v>326.4165079929987</v>
       </c>
       <c r="E97">
-        <v>895.3396810684335</v>
+        <v>906.2717448547469</v>
       </c>
       <c r="F97">
-        <v>1038.546059699766</v>
+        <v>1049.478123486079</v>
       </c>
       <c r="G97">
         <v>6.84</v>
@@ -9241,37 +9241,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M97">
-        <v>244.8891608772048</v>
+        <v>247.4669415180174</v>
       </c>
       <c r="N97">
-        <v>-159.7791608772048</v>
+        <v>-162.3569415180174</v>
       </c>
       <c r="O97">
-        <v>-23.96687413158071</v>
+        <v>-24.35354122770261</v>
       </c>
       <c r="P97">
-        <v>-135.812286745624</v>
+        <v>-138.0034002903148</v>
       </c>
       <c r="Q97">
-        <v>-38.71228674562406</v>
+        <v>-40.90340029031483</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5987397721157737</v>
+        <v>0.7369747151447174</v>
       </c>
       <c r="T97">
-        <v>10.12728611072756</v>
+        <v>12.65910763840946</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05213174790697058</v>
+        <v>0.05158870886627297</v>
       </c>
       <c r="W97">
-        <v>0.2235073338435363</v>
+        <v>0.2236353824493328</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3475449860464705</v>
+        <v>0.3439247257751532</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2441689557571482</v>
+        <v>0.2460689557571482</v>
       </c>
       <c r="C98">
-        <v>-716.2216154930801</v>
+        <v>-729.6985109790554</v>
       </c>
       <c r="D98">
-        <v>326.4165079929988</v>
+        <v>323.8716762933369</v>
       </c>
       <c r="E98">
-        <v>906.2717448547467</v>
+        <v>917.20380864106</v>
       </c>
       <c r="F98">
-        <v>1049.478123486079</v>
+        <v>1060.410187272392</v>
       </c>
       <c r="G98">
         <v>6.84</v>
@@ -9323,37 +9323,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M98">
-        <v>247.4669415180174</v>
+        <v>250.0447221588301</v>
       </c>
       <c r="N98">
-        <v>-162.3569415180174</v>
+        <v>-164.9347221588301</v>
       </c>
       <c r="O98">
-        <v>-24.35354122770261</v>
+        <v>-24.74020832382451</v>
       </c>
       <c r="P98">
-        <v>-138.0034002903148</v>
+        <v>-140.1945138350056</v>
       </c>
       <c r="Q98">
-        <v>-40.90340029031478</v>
+        <v>-43.09451383500559</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7369747151447155</v>
+        <v>0.9673662868596207</v>
       </c>
       <c r="T98">
-        <v>12.65910763840943</v>
+        <v>16.8788101845459</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05158870886627298</v>
+        <v>0.05105686650682687</v>
       </c>
       <c r="W98">
-        <v>0.2236353824493328</v>
+        <v>0.2237607908776902</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3439247257751532</v>
+        <v>0.3403791100455125</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2460689557571482</v>
+        <v>0.2479689557571482</v>
       </c>
       <c r="C99">
-        <v>-729.6985109790554</v>
+        <v>-743.1360330335772</v>
       </c>
       <c r="D99">
-        <v>323.8716762933369</v>
+        <v>321.3662180251284</v>
       </c>
       <c r="E99">
-        <v>917.20380864106</v>
+        <v>928.1358724273734</v>
       </c>
       <c r="F99">
-        <v>1060.410187272392</v>
+        <v>1071.342251058706</v>
       </c>
       <c r="G99">
         <v>6.84</v>
@@ -9405,37 +9405,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M99">
-        <v>250.0447221588301</v>
+        <v>252.6225027996428</v>
       </c>
       <c r="N99">
-        <v>-164.9347221588301</v>
+        <v>-167.5125027996428</v>
       </c>
       <c r="O99">
-        <v>-24.74020832382451</v>
+        <v>-25.12687541994642</v>
       </c>
       <c r="P99">
-        <v>-140.1945138350056</v>
+        <v>-142.3856273796964</v>
       </c>
       <c r="Q99">
-        <v>-43.09451383500559</v>
+        <v>-45.28562737969636</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9673662868596207</v>
+        <v>1.428149430289431</v>
       </c>
       <c r="T99">
-        <v>16.8788101845459</v>
+        <v>25.31821527681885</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05105686650682687</v>
+        <v>0.05053587807308373</v>
       </c>
       <c r="W99">
-        <v>0.2237607908776902</v>
+        <v>0.2238836399503669</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3403791100455125</v>
+        <v>0.3369058538205582</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2479689557571482</v>
+        <v>0.2498689557571482</v>
       </c>
       <c r="C100">
-        <v>-743.1360330335772</v>
+        <v>-756.5350884158415</v>
       </c>
       <c r="D100">
-        <v>321.3662180251284</v>
+        <v>318.8992264291774</v>
       </c>
       <c r="E100">
-        <v>928.1358724273734</v>
+        <v>939.0679362136866</v>
       </c>
       <c r="F100">
-        <v>1071.342251058706</v>
+        <v>1082.274314845019</v>
       </c>
       <c r="G100">
         <v>6.84</v>
@@ -9487,37 +9487,37 @@
         <v>85.11000000000001</v>
       </c>
       <c r="M100">
-        <v>252.6225027996428</v>
+        <v>255.2002834404555</v>
       </c>
       <c r="N100">
-        <v>-167.5125027996428</v>
+        <v>-170.0902834404554</v>
       </c>
       <c r="O100">
-        <v>-25.12687541994642</v>
+        <v>-25.51354251606832</v>
       </c>
       <c r="P100">
-        <v>-142.3856273796964</v>
+        <v>-144.5767409243871</v>
       </c>
       <c r="Q100">
-        <v>-45.28562737969636</v>
+        <v>-47.47674092438712</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.428149430289431</v>
+        <v>2.810498860578862</v>
       </c>
       <c r="T100">
-        <v>25.31821527681885</v>
+        <v>50.6364305536377</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05053587807308373</v>
+        <v>0.0500254146582041</v>
       </c>
       <c r="W100">
-        <v>0.2238836399503669</v>
+        <v>0.2240040072235955</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3369058538205582</v>
+        <v>0.3335027643880274</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2498689557571482</v>
-      </c>
-      <c r="C101">
-        <v>-756.5350884158415</v>
-      </c>
-      <c r="D101">
-        <v>318.8992264291774</v>
-      </c>
-      <c r="E101">
-        <v>939.0679362136866</v>
-      </c>
-      <c r="F101">
-        <v>1082.274314845019</v>
-      </c>
-      <c r="G101">
-        <v>6.84</v>
-      </c>
-      <c r="H101">
-        <v>950</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>182.21</v>
-      </c>
-      <c r="K101">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>85.11000000000001</v>
-      </c>
-      <c r="M101">
-        <v>255.2002834404555</v>
-      </c>
-      <c r="N101">
-        <v>-170.0902834404554</v>
-      </c>
-      <c r="O101">
-        <v>-25.51354251606832</v>
-      </c>
-      <c r="P101">
-        <v>-144.5767409243871</v>
-      </c>
-      <c r="Q101">
-        <v>-47.47674092438712</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.810498860578862</v>
-      </c>
-      <c r="T101">
-        <v>50.6364305536377</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0500254146582041</v>
-      </c>
-      <c r="W101">
-        <v>0.2240040072235955</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3335027643880274</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
